--- a/research/traditional_assets/database/data/kuwait/kuwait_healthcare_support_services.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_healthcare_support_services.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08923958868186335</v>
+        <v>0.08914397929884056</v>
       </c>
       <c r="C2">
-        <v>935.8294269543271</v>
+        <v>928.9385157950895</v>
       </c>
       <c r="D2">
-        <v>920.3294269543271</v>
+        <v>922.3595157950896</v>
       </c>
       <c r="E2">
-        <v>-702.8</v>
+        <v>-693.8789999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>8.920999999999999</v>
       </c>
       <c r="G2">
         <v>15.5</v>
@@ -1451,28 +1451,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4487263</v>
       </c>
       <c r="N2">
-        <v>65.66666666666667</v>
+        <v>65.21794036666667</v>
       </c>
       <c r="O2">
-        <v>9.85</v>
+        <v>9.782691054999999</v>
       </c>
       <c r="P2">
-        <v>55.81666666666667</v>
+        <v>55.43524931166667</v>
       </c>
       <c r="Q2">
-        <v>84.81666666666666</v>
+        <v>84.43524931166667</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08923958868186335</v>
+        <v>0.0896125548473137</v>
       </c>
       <c r="T2">
-        <v>0.8240329453738455</v>
+        <v>0.8311079757129138</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>146.3401335439146</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08914397929884056</v>
+        <v>0.08904836991581777</v>
       </c>
       <c r="C3">
-        <v>928.9385157950895</v>
+        <v>922.0565804905226</v>
       </c>
       <c r="D3">
-        <v>922.3595157950896</v>
+        <v>924.3985804905226</v>
       </c>
       <c r="E3">
-        <v>-693.8789999999999</v>
+        <v>-684.958</v>
       </c>
       <c r="F3">
-        <v>8.920999999999999</v>
+        <v>17.842</v>
       </c>
       <c r="G3">
         <v>15.5</v>
@@ -1533,28 +1533,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M3">
-        <v>0.4487263</v>
+        <v>0.8974525999999999</v>
       </c>
       <c r="N3">
-        <v>65.21794036666667</v>
+        <v>64.76921406666668</v>
       </c>
       <c r="O3">
-        <v>9.782691054999999</v>
+        <v>9.715382110000002</v>
       </c>
       <c r="P3">
-        <v>55.43524931166667</v>
+        <v>55.05383195666668</v>
       </c>
       <c r="Q3">
-        <v>84.43524931166667</v>
+        <v>84.05383195666667</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0896125548473137</v>
+        <v>0.08999313256716099</v>
       </c>
       <c r="T3">
-        <v>0.8311079757129138</v>
+        <v>0.838327394426249</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>146.3401335439146</v>
+        <v>73.17006677195729</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08904836991581777</v>
+        <v>0.08895276053279495</v>
       </c>
       <c r="C4">
-        <v>922.0565804905226</v>
+        <v>915.1836807014164</v>
       </c>
       <c r="D4">
-        <v>924.3985804905226</v>
+        <v>926.4466807014164</v>
       </c>
       <c r="E4">
-        <v>-684.958</v>
+        <v>-676.0369999999999</v>
       </c>
       <c r="F4">
-        <v>17.842</v>
+        <v>26.76299999999999</v>
       </c>
       <c r="G4">
         <v>15.5</v>
@@ -1615,28 +1615,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M4">
-        <v>0.8974525999999999</v>
+        <v>1.3461789</v>
       </c>
       <c r="N4">
-        <v>64.76921406666668</v>
+        <v>64.32048776666667</v>
       </c>
       <c r="O4">
-        <v>9.715382110000002</v>
+        <v>9.648073165000001</v>
       </c>
       <c r="P4">
-        <v>55.05383195666668</v>
+        <v>54.67241460166667</v>
       </c>
       <c r="Q4">
-        <v>84.05383195666667</v>
+        <v>83.67241460166667</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08999313256716099</v>
+        <v>0.09038155725030408</v>
       </c>
       <c r="T4">
-        <v>0.838327394426249</v>
+        <v>0.8456956671336734</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>73.17006677195729</v>
+        <v>48.7800445146382</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08895276053279495</v>
+        <v>0.08885715114977218</v>
       </c>
       <c r="C5">
-        <v>915.1836807014164</v>
+        <v>908.3198766184722</v>
       </c>
       <c r="D5">
-        <v>926.4466807014164</v>
+        <v>928.5038766184722</v>
       </c>
       <c r="E5">
-        <v>-676.0369999999999</v>
+        <v>-667.116</v>
       </c>
       <c r="F5">
-        <v>26.76299999999999</v>
+        <v>35.684</v>
       </c>
       <c r="G5">
         <v>15.5</v>
@@ -1697,28 +1697,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M5">
-        <v>1.3461789</v>
+        <v>1.7949052</v>
       </c>
       <c r="N5">
-        <v>64.32048776666667</v>
+        <v>63.87176146666667</v>
       </c>
       <c r="O5">
-        <v>9.648073165000001</v>
+        <v>9.580764220000001</v>
       </c>
       <c r="P5">
-        <v>54.67241460166667</v>
+        <v>54.29099724666667</v>
       </c>
       <c r="Q5">
-        <v>83.67241460166667</v>
+        <v>83.29099724666668</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09038155725030408</v>
+        <v>0.09077807411434602</v>
       </c>
       <c r="T5">
-        <v>0.8456956671336734</v>
+        <v>0.8532174455225026</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>48.7800445146382</v>
+        <v>36.58503338597864</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08885715114977218</v>
+        <v>0.08876154176674939</v>
       </c>
       <c r="C6">
-        <v>908.3198766184722</v>
+        <v>901.4652289682025</v>
       </c>
       <c r="D6">
-        <v>928.5038766184722</v>
+        <v>930.5702289682025</v>
       </c>
       <c r="E6">
-        <v>-667.116</v>
+        <v>-658.1949999999999</v>
       </c>
       <c r="F6">
-        <v>35.684</v>
+        <v>44.605</v>
       </c>
       <c r="G6">
         <v>15.5</v>
@@ -1779,28 +1779,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M6">
-        <v>1.7949052</v>
+        <v>2.2436315</v>
       </c>
       <c r="N6">
-        <v>63.87176146666667</v>
+        <v>63.42303516666667</v>
       </c>
       <c r="O6">
-        <v>9.580764220000001</v>
+        <v>9.513455275</v>
       </c>
       <c r="P6">
-        <v>54.29099724666667</v>
+        <v>53.90957989166667</v>
       </c>
       <c r="Q6">
-        <v>83.29099724666668</v>
+        <v>82.90957989166668</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09077807411434602</v>
+        <v>0.09118293870184146</v>
       </c>
       <c r="T6">
-        <v>0.8532174455225026</v>
+        <v>0.8608975771405702</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>36.58503338597864</v>
+        <v>29.26802670878292</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08876154176674939</v>
+        <v>0.08866593238372658</v>
       </c>
       <c r="C7">
-        <v>901.4652289682025</v>
+        <v>894.6197990189037</v>
       </c>
       <c r="D7">
-        <v>930.5702289682025</v>
+        <v>932.6457990189036</v>
       </c>
       <c r="E7">
-        <v>-658.1949999999999</v>
+        <v>-649.274</v>
       </c>
       <c r="F7">
-        <v>44.605</v>
+        <v>53.526</v>
       </c>
       <c r="G7">
         <v>15.5</v>
@@ -1861,28 +1861,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M7">
-        <v>2.2436315</v>
+        <v>2.692357799999999</v>
       </c>
       <c r="N7">
-        <v>63.42303516666667</v>
+        <v>62.97430886666668</v>
       </c>
       <c r="O7">
-        <v>9.513455275</v>
+        <v>9.446146330000001</v>
       </c>
       <c r="P7">
-        <v>53.90957989166667</v>
+        <v>53.52816253666667</v>
       </c>
       <c r="Q7">
-        <v>82.90957989166668</v>
+        <v>82.52816253666667</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09118293870184146</v>
+        <v>0.09159641742949637</v>
       </c>
       <c r="T7">
-        <v>0.8608975771405702</v>
+        <v>0.8687411158143413</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>29.26802670878292</v>
+        <v>24.3900222573191</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08866593238372658</v>
+        <v>0.08857032300070379</v>
       </c>
       <c r="C8">
-        <v>894.6197990189037</v>
+        <v>887.7836485867108</v>
       </c>
       <c r="D8">
-        <v>932.6457990189036</v>
+        <v>934.7306485867108</v>
       </c>
       <c r="E8">
-        <v>-649.274</v>
+        <v>-640.353</v>
       </c>
       <c r="F8">
-        <v>53.52599999999999</v>
+        <v>62.44699999999999</v>
       </c>
       <c r="G8">
         <v>15.5</v>
@@ -1943,28 +1943,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M8">
-        <v>2.692357799999999</v>
+        <v>3.141084099999999</v>
       </c>
       <c r="N8">
-        <v>62.97430886666668</v>
+        <v>62.52558256666667</v>
       </c>
       <c r="O8">
-        <v>9.446146330000001</v>
+        <v>9.378837385000001</v>
       </c>
       <c r="P8">
-        <v>53.52816253666667</v>
+        <v>53.14674518166667</v>
       </c>
       <c r="Q8">
-        <v>82.52816253666667</v>
+        <v>82.14674518166667</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09159641742949637</v>
+        <v>0.09201878817279976</v>
       </c>
       <c r="T8">
-        <v>0.8687411158143413</v>
+        <v>0.8767533327391615</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.3900222573191</v>
+        <v>20.90573336341637</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08857032300070378</v>
+        <v>0.088474713617681</v>
       </c>
       <c r="C9">
-        <v>887.7836485867113</v>
+        <v>880.9568400417379</v>
       </c>
       <c r="D9">
-        <v>934.7306485867113</v>
+        <v>936.8248400417378</v>
       </c>
       <c r="E9">
-        <v>-640.353</v>
+        <v>-631.432</v>
       </c>
       <c r="F9">
-        <v>62.447</v>
+        <v>71.36799999999999</v>
       </c>
       <c r="G9">
         <v>15.5</v>
@@ -2025,28 +2025,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M9">
-        <v>3.1410841</v>
+        <v>3.5898104</v>
       </c>
       <c r="N9">
-        <v>62.52558256666667</v>
+        <v>62.07685626666667</v>
       </c>
       <c r="O9">
-        <v>9.378837385000001</v>
+        <v>9.31152844</v>
       </c>
       <c r="P9">
-        <v>53.14674518166667</v>
+        <v>52.76532782666668</v>
       </c>
       <c r="Q9">
-        <v>82.14674518166667</v>
+        <v>81.76532782666668</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09201878817279976</v>
+        <v>0.09245034088878369</v>
       </c>
       <c r="T9">
-        <v>0.8767533327391615</v>
+        <v>0.884939728292782</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.90573336341637</v>
+        <v>18.29251669298932</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.088474713617681</v>
+        <v>0.0883791042346582</v>
       </c>
       <c r="C10">
-        <v>880.9568400417379</v>
+        <v>874.1394363142945</v>
       </c>
       <c r="D10">
-        <v>936.8248400417378</v>
+        <v>938.9284363142945</v>
       </c>
       <c r="E10">
-        <v>-631.432</v>
+        <v>-622.511</v>
       </c>
       <c r="F10">
-        <v>71.36799999999999</v>
+        <v>80.28899999999999</v>
       </c>
       <c r="G10">
         <v>15.5</v>
@@ -2107,28 +2107,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M10">
-        <v>3.5898104</v>
+        <v>4.038536699999999</v>
       </c>
       <c r="N10">
-        <v>62.07685626666667</v>
+        <v>61.62812996666667</v>
       </c>
       <c r="O10">
-        <v>9.31152844</v>
+        <v>9.244219494999999</v>
       </c>
       <c r="P10">
-        <v>52.76532782666668</v>
+        <v>52.38391047166667</v>
       </c>
       <c r="Q10">
-        <v>81.76532782666668</v>
+        <v>81.38391047166667</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09245034088878369</v>
+        <v>0.09289137827984417</v>
       </c>
       <c r="T10">
-        <v>0.884939728292782</v>
+        <v>0.8933060446278006</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.29251669298932</v>
+        <v>16.26001483821273</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0883791042346582</v>
+        <v>0.08828349485163542</v>
       </c>
       <c r="C11">
-        <v>874.1394363142945</v>
+        <v>867.3315009011901</v>
       </c>
       <c r="D11">
-        <v>938.9284363142945</v>
+        <v>941.04150090119</v>
       </c>
       <c r="E11">
-        <v>-622.511</v>
+        <v>-613.5899999999999</v>
       </c>
       <c r="F11">
-        <v>80.28899999999999</v>
+        <v>89.20999999999998</v>
       </c>
       <c r="G11">
         <v>15.5</v>
@@ -2189,28 +2189,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M11">
-        <v>4.038536699999999</v>
+        <v>4.487262999999999</v>
       </c>
       <c r="N11">
-        <v>61.62812996666667</v>
+        <v>61.17940366666667</v>
       </c>
       <c r="O11">
-        <v>9.244219494999999</v>
+        <v>9.176910550000001</v>
       </c>
       <c r="P11">
-        <v>52.38391047166667</v>
+        <v>52.00249311666667</v>
       </c>
       <c r="Q11">
-        <v>81.38391047166667</v>
+        <v>81.00249311666667</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09289137827984417</v>
+        <v>0.09334221650181712</v>
       </c>
       <c r="T11">
-        <v>0.8933060446278006</v>
+        <v>0.9018582791035977</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.26001483821273</v>
+        <v>14.63401335439146</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08828349485163542</v>
+        <v>0.08818788546861261</v>
       </c>
       <c r="C12">
-        <v>867.33150090119</v>
+        <v>860.5330978721249</v>
       </c>
       <c r="D12">
-        <v>941.04150090119</v>
+        <v>943.1640978721249</v>
       </c>
       <c r="E12">
-        <v>-613.5899999999999</v>
+        <v>-604.669</v>
       </c>
       <c r="F12">
-        <v>89.20999999999999</v>
+        <v>98.13099999999999</v>
       </c>
       <c r="G12">
         <v>15.5</v>
@@ -2271,28 +2271,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M12">
-        <v>4.487263</v>
+        <v>4.935989299999999</v>
       </c>
       <c r="N12">
-        <v>61.17940366666667</v>
+        <v>60.73067736666667</v>
       </c>
       <c r="O12">
-        <v>9.176910550000001</v>
+        <v>9.109601605</v>
       </c>
       <c r="P12">
-        <v>52.00249311666667</v>
+        <v>51.62107576166667</v>
       </c>
       <c r="Q12">
-        <v>81.00249311666667</v>
+        <v>80.62107576166667</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09334221650181712</v>
+        <v>0.09380318591978945</v>
       </c>
       <c r="T12">
-        <v>0.9018582791035977</v>
+        <v>0.9106026986237945</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.63401335439146</v>
+        <v>13.30364850399224</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08818788546861261</v>
+        <v>0.08824527608558981</v>
       </c>
       <c r="C13">
-        <v>860.5330978721249</v>
+        <v>850.3368377141164</v>
       </c>
       <c r="D13">
-        <v>943.1640978721249</v>
+        <v>941.8888377141164</v>
       </c>
       <c r="E13">
-        <v>-604.669</v>
+        <v>-595.7479999999999</v>
       </c>
       <c r="F13">
-        <v>98.13099999999999</v>
+        <v>107.052</v>
       </c>
       <c r="G13">
         <v>15.5</v>
@@ -2353,45 +2353,45 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M13">
-        <v>4.935989299999999</v>
+        <v>5.545293599999999</v>
       </c>
       <c r="N13">
-        <v>60.73067736666667</v>
+        <v>60.12137306666667</v>
       </c>
       <c r="O13">
-        <v>9.109601605</v>
+        <v>9.01820596</v>
       </c>
       <c r="P13">
-        <v>51.62107576166667</v>
+        <v>51.10316710666667</v>
       </c>
       <c r="Q13">
-        <v>80.62107576166667</v>
+        <v>80.10316710666667</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09380318591978945</v>
+        <v>0.09427463191544297</v>
       </c>
       <c r="T13">
-        <v>0.9106026986237945</v>
+        <v>0.9195458549512686</v>
       </c>
       <c r="U13">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V13">
         <v>0.15</v>
       </c>
       <c r="W13">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y13">
-        <v>13.30364850399224</v>
+        <v>11.841873740764</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08824527608558981</v>
+        <v>0.08816241670256701</v>
       </c>
       <c r="C14">
-        <v>850.3368377141164</v>
+        <v>843.2581388395932</v>
       </c>
       <c r="D14">
-        <v>941.8888377141164</v>
+        <v>943.7311388395932</v>
       </c>
       <c r="E14">
-        <v>-595.7479999999999</v>
+        <v>-586.827</v>
       </c>
       <c r="F14">
-        <v>107.052</v>
+        <v>115.973</v>
       </c>
       <c r="G14">
         <v>15.5</v>
@@ -2435,28 +2435,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M14">
-        <v>5.545293599999999</v>
+        <v>6.0074014</v>
       </c>
       <c r="N14">
-        <v>60.12137306666667</v>
+        <v>59.65926526666667</v>
       </c>
       <c r="O14">
-        <v>9.01820596</v>
+        <v>8.948889790000001</v>
       </c>
       <c r="P14">
-        <v>51.10316710666667</v>
+        <v>50.71037547666667</v>
       </c>
       <c r="Q14">
-        <v>80.10316710666667</v>
+        <v>79.71037547666667</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09427463191544297</v>
+        <v>0.09475691575007703</v>
       </c>
       <c r="T14">
-        <v>0.9195458549512686</v>
+        <v>0.9286946010793742</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.841873740764</v>
+        <v>10.93096037608985</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08816241670256701</v>
+        <v>0.0880795573195442</v>
       </c>
       <c r="C15">
-        <v>843.2581388395932</v>
+        <v>836.1866610404209</v>
       </c>
       <c r="D15">
-        <v>943.7311388395932</v>
+        <v>945.5806610404209</v>
       </c>
       <c r="E15">
-        <v>-586.827</v>
+        <v>-577.9059999999999</v>
       </c>
       <c r="F15">
-        <v>115.973</v>
+        <v>124.894</v>
       </c>
       <c r="G15">
         <v>15.5</v>
@@ -2517,28 +2517,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M15">
-        <v>6.0074014</v>
+        <v>6.4695092</v>
       </c>
       <c r="N15">
-        <v>59.65926526666667</v>
+        <v>59.19715746666667</v>
       </c>
       <c r="O15">
-        <v>8.948889790000001</v>
+        <v>8.87957362</v>
       </c>
       <c r="P15">
-        <v>50.71037547666667</v>
+        <v>50.31758384666667</v>
       </c>
       <c r="Q15">
-        <v>79.71037547666667</v>
+        <v>79.31758384666668</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09475691575007703</v>
+        <v>0.0952504154878421</v>
       </c>
       <c r="T15">
-        <v>0.9286946010793742</v>
+        <v>0.9380561087453426</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>10.93096037608985</v>
+        <v>10.15017749208343</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0880795573195442</v>
+        <v>0.08821344793652143</v>
       </c>
       <c r="C16">
-        <v>836.1866610404209</v>
+        <v>824.2806554757253</v>
       </c>
       <c r="D16">
-        <v>945.5806610404209</v>
+        <v>942.5956554757254</v>
       </c>
       <c r="E16">
-        <v>-577.9059999999999</v>
+        <v>-568.9849999999999</v>
       </c>
       <c r="F16">
-        <v>124.894</v>
+        <v>133.815</v>
       </c>
       <c r="G16">
         <v>15.5</v>
@@ -2599,45 +2599,45 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M16">
-        <v>6.4695092</v>
+        <v>7.159102499999999</v>
       </c>
       <c r="N16">
-        <v>59.19715746666667</v>
+        <v>58.50756416666667</v>
       </c>
       <c r="O16">
-        <v>8.87957362</v>
+        <v>8.776134624999999</v>
       </c>
       <c r="P16">
-        <v>50.31758384666667</v>
+        <v>49.73142954166667</v>
       </c>
       <c r="Q16">
-        <v>79.31758384666668</v>
+        <v>78.73142954166667</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0952504154878421</v>
+        <v>0.09575552698414286</v>
       </c>
       <c r="T16">
-        <v>0.9380561087453426</v>
+        <v>0.9476378871799223</v>
       </c>
       <c r="U16">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V16">
         <v>0.15</v>
       </c>
       <c r="W16">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y16">
-        <v>10.15017749208343</v>
+        <v>9.172471921817948</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08821344793652143</v>
+        <v>0.08814503855349864</v>
       </c>
       <c r="C17">
-        <v>824.2806554757254</v>
+        <v>816.8824404213474</v>
       </c>
       <c r="D17">
-        <v>942.5956554757254</v>
+        <v>944.1184404213474</v>
       </c>
       <c r="E17">
-        <v>-568.985</v>
+        <v>-560.064</v>
       </c>
       <c r="F17">
-        <v>133.815</v>
+        <v>142.736</v>
       </c>
       <c r="G17">
         <v>15.5</v>
@@ -2681,28 +2681,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M17">
-        <v>7.159102499999999</v>
+        <v>7.636375999999999</v>
       </c>
       <c r="N17">
-        <v>58.50756416666668</v>
+        <v>58.03029066666667</v>
       </c>
       <c r="O17">
-        <v>8.776134625000001</v>
+        <v>8.704543600000001</v>
       </c>
       <c r="P17">
-        <v>49.73142954166667</v>
+        <v>49.32574706666667</v>
       </c>
       <c r="Q17">
-        <v>78.73142954166667</v>
+        <v>78.32574706666668</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09575552698414286</v>
+        <v>0.09627266494464123</v>
       </c>
       <c r="T17">
-        <v>0.9476378871799223</v>
+        <v>0.9574478031962778</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.17247192181795</v>
+        <v>8.599192426704327</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08814503855349864</v>
+        <v>0.08807662917047583</v>
       </c>
       <c r="C18">
-        <v>816.8824404213474</v>
+        <v>809.4891535166664</v>
       </c>
       <c r="D18">
-        <v>944.1184404213474</v>
+        <v>945.6461535166665</v>
       </c>
       <c r="E18">
-        <v>-560.064</v>
+        <v>-551.143</v>
       </c>
       <c r="F18">
-        <v>142.736</v>
+        <v>151.657</v>
       </c>
       <c r="G18">
         <v>15.5</v>
@@ -2763,28 +2763,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M18">
-        <v>7.636375999999999</v>
+        <v>8.113649499999999</v>
       </c>
       <c r="N18">
-        <v>58.03029066666667</v>
+        <v>57.55301716666667</v>
       </c>
       <c r="O18">
-        <v>8.704543600000001</v>
+        <v>8.632952575000001</v>
       </c>
       <c r="P18">
-        <v>49.32574706666667</v>
+        <v>48.92006459166667</v>
       </c>
       <c r="Q18">
-        <v>78.32574706666668</v>
+        <v>77.92006459166667</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09627266494464123</v>
+        <v>0.09680226406081427</v>
       </c>
       <c r="T18">
-        <v>0.9574478031962778</v>
+        <v>0.9674941027310994</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.599192426704327</v>
+        <v>8.093357578074659</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08807662917047583</v>
+        <v>0.08800821978745303</v>
       </c>
       <c r="C19">
-        <v>809.4891535166664</v>
+        <v>802.1008187237217</v>
       </c>
       <c r="D19">
-        <v>945.6461535166665</v>
+        <v>947.1788187237216</v>
       </c>
       <c r="E19">
-        <v>-551.143</v>
+        <v>-542.222</v>
       </c>
       <c r="F19">
-        <v>151.657</v>
+        <v>160.578</v>
       </c>
       <c r="G19">
         <v>15.5</v>
@@ -2845,28 +2845,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M19">
-        <v>8.113649499999999</v>
+        <v>8.590923</v>
       </c>
       <c r="N19">
-        <v>57.55301716666667</v>
+        <v>57.07574366666667</v>
       </c>
       <c r="O19">
-        <v>8.632952575000001</v>
+        <v>8.561361549999999</v>
       </c>
       <c r="P19">
-        <v>48.92006459166667</v>
+        <v>48.51438211666667</v>
       </c>
       <c r="Q19">
-        <v>77.92006459166667</v>
+        <v>77.51438211666667</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09680226406081427</v>
+        <v>0.09734478022860127</v>
       </c>
       <c r="T19">
-        <v>0.9674941027310994</v>
+        <v>0.9777854339618922</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.093357578074659</v>
+        <v>7.643726601514955</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08800821978745305</v>
+        <v>0.08806901040443026</v>
       </c>
       <c r="C20">
-        <v>802.1008187237212</v>
+        <v>791.8176012450757</v>
       </c>
       <c r="D20">
-        <v>947.1788187237212</v>
+        <v>945.8166012450757</v>
       </c>
       <c r="E20">
-        <v>-542.222</v>
+        <v>-533.3009999999999</v>
       </c>
       <c r="F20">
-        <v>160.578</v>
+        <v>169.499</v>
       </c>
       <c r="G20">
         <v>15.5</v>
@@ -2927,45 +2927,45 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M20">
-        <v>8.590922999999998</v>
+        <v>9.203795700000001</v>
       </c>
       <c r="N20">
-        <v>57.07574366666667</v>
+        <v>56.46287096666667</v>
       </c>
       <c r="O20">
-        <v>8.561361550000001</v>
+        <v>8.469430645000001</v>
       </c>
       <c r="P20">
-        <v>48.51438211666667</v>
+        <v>47.99344032166667</v>
       </c>
       <c r="Q20">
-        <v>77.51438211666667</v>
+        <v>76.99344032166667</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09734478022860127</v>
+        <v>0.0979006918573213</v>
       </c>
       <c r="T20">
-        <v>0.9777854339618922</v>
+        <v>0.9883308721366554</v>
       </c>
       <c r="U20">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V20">
         <v>0.15</v>
       </c>
       <c r="W20">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y20">
-        <v>7.643726601514958</v>
+        <v>7.134737537325679</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08806901040443026</v>
+        <v>0.08800740102140746</v>
       </c>
       <c r="C21">
-        <v>791.8176012450757</v>
+        <v>784.2771927016754</v>
       </c>
       <c r="D21">
-        <v>945.8166012450757</v>
+        <v>947.1971927016754</v>
       </c>
       <c r="E21">
-        <v>-533.3009999999999</v>
+        <v>-524.38</v>
       </c>
       <c r="F21">
-        <v>169.499</v>
+        <v>178.42</v>
       </c>
       <c r="G21">
         <v>15.5</v>
@@ -3009,28 +3009,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M21">
-        <v>9.203795700000001</v>
+        <v>9.688205999999999</v>
       </c>
       <c r="N21">
-        <v>56.46287096666667</v>
+        <v>55.97846066666667</v>
       </c>
       <c r="O21">
-        <v>8.469430645000001</v>
+        <v>8.3967691</v>
       </c>
       <c r="P21">
-        <v>47.99344032166667</v>
+        <v>47.58169156666667</v>
       </c>
       <c r="Q21">
-        <v>76.99344032166667</v>
+        <v>76.58169156666668</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.0979006918573213</v>
+        <v>0.09847050127675931</v>
       </c>
       <c r="T21">
-        <v>0.9883308721366554</v>
+        <v>0.9991399462657876</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.134737537325679</v>
+        <v>6.778000660459395</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08800740102140746</v>
+        <v>0.08794579163838467</v>
       </c>
       <c r="C22">
-        <v>784.2771927016754</v>
+        <v>776.740820499012</v>
       </c>
       <c r="D22">
-        <v>947.1971927016754</v>
+        <v>948.581820499012</v>
       </c>
       <c r="E22">
-        <v>-524.38</v>
+        <v>-515.4589999999999</v>
       </c>
       <c r="F22">
-        <v>178.42</v>
+        <v>187.341</v>
       </c>
       <c r="G22">
         <v>15.5</v>
@@ -3091,28 +3091,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M22">
-        <v>9.688205999999999</v>
+        <v>10.1726163</v>
       </c>
       <c r="N22">
-        <v>55.97846066666667</v>
+        <v>55.49405036666667</v>
       </c>
       <c r="O22">
-        <v>8.3967691</v>
+        <v>8.324107554999999</v>
       </c>
       <c r="P22">
-        <v>47.58169156666667</v>
+        <v>47.16994281166667</v>
       </c>
       <c r="Q22">
-        <v>76.58169156666668</v>
+        <v>76.16994281166667</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09847050127675931</v>
+        <v>0.09905473625111982</v>
       </c>
       <c r="T22">
-        <v>0.9991399462657876</v>
+        <v>1.010222667841227</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.778000660459395</v>
+        <v>6.455238724247041</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08794579163838466</v>
+        <v>0.08788418225536186</v>
       </c>
       <c r="C23">
-        <v>776.7408204990123</v>
+        <v>769.20850236416</v>
       </c>
       <c r="D23">
-        <v>948.5818204990123</v>
+        <v>949.97050236416</v>
       </c>
       <c r="E23">
-        <v>-515.4589999999999</v>
+        <v>-506.538</v>
       </c>
       <c r="F23">
-        <v>187.341</v>
+        <v>196.262</v>
       </c>
       <c r="G23">
         <v>15.5</v>
@@ -3173,28 +3173,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M23">
-        <v>10.1726163</v>
+        <v>10.6570266</v>
       </c>
       <c r="N23">
-        <v>55.49405036666667</v>
+        <v>55.00964006666668</v>
       </c>
       <c r="O23">
-        <v>8.324107554999999</v>
+        <v>8.25144601</v>
       </c>
       <c r="P23">
-        <v>47.16994281166667</v>
+        <v>46.75819405666667</v>
       </c>
       <c r="Q23">
-        <v>76.16994281166667</v>
+        <v>75.75819405666667</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09905473625111982</v>
+        <v>0.09965395160943828</v>
       </c>
       <c r="T23">
-        <v>1.010222667841227</v>
+        <v>1.021589561764755</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>6.455238724247042</v>
+        <v>6.161818782235815</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08788418225536186</v>
+        <v>0.08801807287233909</v>
       </c>
       <c r="C24">
-        <v>769.20850236416</v>
+        <v>757.2747609475558</v>
       </c>
       <c r="D24">
-        <v>949.97050236416</v>
+        <v>946.9577609475558</v>
       </c>
       <c r="E24">
-        <v>-506.538</v>
+        <v>-497.617</v>
       </c>
       <c r="F24">
-        <v>196.262</v>
+        <v>205.183</v>
       </c>
       <c r="G24">
         <v>15.5</v>
@@ -3255,45 +3255,45 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M24">
-        <v>10.6570266</v>
+        <v>11.3466199</v>
       </c>
       <c r="N24">
-        <v>55.00964006666668</v>
+        <v>54.32004676666667</v>
       </c>
       <c r="O24">
-        <v>8.25144601</v>
+        <v>8.148007015000001</v>
       </c>
       <c r="P24">
-        <v>46.75819405666667</v>
+        <v>46.17203975166667</v>
       </c>
       <c r="Q24">
-        <v>75.75819405666667</v>
+        <v>75.17203975166667</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09965395160943828</v>
+        <v>0.1002687310030378</v>
       </c>
       <c r="T24">
-        <v>1.021589561764755</v>
+        <v>1.033251699686296</v>
       </c>
       <c r="U24">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V24">
         <v>0.15</v>
       </c>
       <c r="W24">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y24">
-        <v>6.161818782235815</v>
+        <v>5.787332901375032</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08801807287233909</v>
+        <v>0.08796496348931628</v>
       </c>
       <c r="C25">
-        <v>757.2747609475558</v>
+        <v>749.5465128977701</v>
       </c>
       <c r="D25">
-        <v>946.9577609475558</v>
+        <v>948.15051289777</v>
       </c>
       <c r="E25">
-        <v>-497.617</v>
+        <v>-488.696</v>
       </c>
       <c r="F25">
-        <v>205.183</v>
+        <v>214.104</v>
       </c>
       <c r="G25">
         <v>15.5</v>
@@ -3337,28 +3337,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M25">
-        <v>11.3466199</v>
+        <v>11.8399512</v>
       </c>
       <c r="N25">
-        <v>54.32004676666667</v>
+        <v>53.82671546666667</v>
       </c>
       <c r="O25">
-        <v>8.148007015000001</v>
+        <v>8.07400732</v>
       </c>
       <c r="P25">
-        <v>46.17203975166667</v>
+        <v>45.75270814666667</v>
       </c>
       <c r="Q25">
-        <v>75.17203975166667</v>
+        <v>74.75270814666666</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1002687310030378</v>
+        <v>0.1008996888017319</v>
       </c>
       <c r="T25">
-        <v>1.033251699686296</v>
+        <v>1.045220735974193</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.787332901375032</v>
+        <v>5.546194030484405</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08796496348931628</v>
+        <v>0.08791185410629347</v>
       </c>
       <c r="C26">
-        <v>749.5465128977701</v>
+        <v>741.8212733272597</v>
       </c>
       <c r="D26">
-        <v>948.15051289777</v>
+        <v>949.3462733272597</v>
       </c>
       <c r="E26">
-        <v>-488.696</v>
+        <v>-479.775</v>
       </c>
       <c r="F26">
-        <v>214.104</v>
+        <v>223.025</v>
       </c>
       <c r="G26">
         <v>15.5</v>
@@ -3419,28 +3419,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M26">
-        <v>11.8399512</v>
+        <v>12.3332825</v>
       </c>
       <c r="N26">
-        <v>53.82671546666667</v>
+        <v>53.33338416666668</v>
       </c>
       <c r="O26">
-        <v>8.07400732</v>
+        <v>8.000007625</v>
       </c>
       <c r="P26">
-        <v>45.75270814666667</v>
+        <v>45.33337654166667</v>
       </c>
       <c r="Q26">
-        <v>74.75270814666666</v>
+        <v>74.33337654166667</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1008996888017319</v>
+        <v>0.1015474721417246</v>
       </c>
       <c r="T26">
-        <v>1.045220735974193</v>
+        <v>1.057508946563102</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.546194030484406</v>
+        <v>5.32434626926503</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08791185410629347</v>
+        <v>0.08785874472327068</v>
       </c>
       <c r="C27">
-        <v>741.8212733272597</v>
+        <v>734.0990536328331</v>
       </c>
       <c r="D27">
-        <v>949.3462733272597</v>
+        <v>950.5450536328332</v>
       </c>
       <c r="E27">
-        <v>-479.775</v>
+        <v>-470.8539999999999</v>
       </c>
       <c r="F27">
-        <v>223.025</v>
+        <v>231.946</v>
       </c>
       <c r="G27">
         <v>15.5</v>
@@ -3501,28 +3501,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M27">
-        <v>12.3332825</v>
+        <v>12.8266138</v>
       </c>
       <c r="N27">
-        <v>53.33338416666668</v>
+        <v>52.84005286666667</v>
       </c>
       <c r="O27">
-        <v>8.000007625</v>
+        <v>7.92600793</v>
       </c>
       <c r="P27">
-        <v>45.33337654166667</v>
+        <v>44.91404493666667</v>
       </c>
       <c r="Q27">
-        <v>74.33337654166667</v>
+        <v>73.91404493666667</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1015474721417246</v>
+        <v>0.102212763139555</v>
       </c>
       <c r="T27">
-        <v>1.057508946563102</v>
+        <v>1.07012927095171</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.32434626926503</v>
+        <v>5.119563720447143</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08785874472327068</v>
+        <v>0.08780563534024789</v>
       </c>
       <c r="C28">
-        <v>734.0990536328331</v>
+        <v>726.3798652689361</v>
       </c>
       <c r="D28">
-        <v>950.5450536328332</v>
+        <v>951.7468652689361</v>
       </c>
       <c r="E28">
-        <v>-470.8539999999999</v>
+        <v>-461.933</v>
       </c>
       <c r="F28">
-        <v>231.946</v>
+        <v>240.867</v>
       </c>
       <c r="G28">
         <v>15.5</v>
@@ -3583,28 +3583,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M28">
-        <v>12.8266138</v>
+        <v>13.3199451</v>
       </c>
       <c r="N28">
-        <v>52.84005286666667</v>
+        <v>52.34672156666667</v>
       </c>
       <c r="O28">
-        <v>7.92600793</v>
+        <v>7.852008235</v>
       </c>
       <c r="P28">
-        <v>44.91404493666667</v>
+        <v>44.49471333166667</v>
       </c>
       <c r="Q28">
-        <v>73.91404493666667</v>
+        <v>73.49471333166667</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.102212763139555</v>
+        <v>0.1028962812880108</v>
       </c>
       <c r="T28">
-        <v>1.07012927095171</v>
+        <v>1.083095357652335</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.119563720447143</v>
+        <v>4.929950249319472</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08780563534024789</v>
+        <v>0.0877525259572251</v>
       </c>
       <c r="C29">
-        <v>726.3798652689361</v>
+        <v>718.6637197480167</v>
       </c>
       <c r="D29">
-        <v>951.7468652689361</v>
+        <v>952.9517197480167</v>
       </c>
       <c r="E29">
-        <v>-461.933</v>
+        <v>-453.0119999999999</v>
       </c>
       <c r="F29">
-        <v>240.867</v>
+        <v>249.788</v>
       </c>
       <c r="G29">
         <v>15.5</v>
@@ -3665,28 +3665,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M29">
-        <v>13.3199451</v>
+        <v>13.8132764</v>
       </c>
       <c r="N29">
-        <v>52.34672156666667</v>
+        <v>51.85339026666667</v>
       </c>
       <c r="O29">
-        <v>7.852008235</v>
+        <v>7.77800854</v>
       </c>
       <c r="P29">
-        <v>44.49471333166667</v>
+        <v>44.07538172666667</v>
       </c>
       <c r="Q29">
-        <v>73.49471333166667</v>
+        <v>73.07538172666668</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1028962812880108</v>
+        <v>0.1035987860517015</v>
       </c>
       <c r="T29">
-        <v>1.083095357652335</v>
+        <v>1.096421613427978</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.929950249319472</v>
+        <v>4.753880597558061</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0877525259572251</v>
+        <v>0.0876994165742023</v>
       </c>
       <c r="C30">
-        <v>718.6637197480167</v>
+        <v>710.9506286408937</v>
       </c>
       <c r="D30">
-        <v>952.9517197480167</v>
+        <v>954.1596286408936</v>
       </c>
       <c r="E30">
-        <v>-453.0119999999999</v>
+        <v>-444.091</v>
       </c>
       <c r="F30">
-        <v>249.788</v>
+        <v>258.709</v>
       </c>
       <c r="G30">
         <v>15.5</v>
@@ -3747,28 +3747,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M30">
-        <v>13.8132764</v>
+        <v>14.3066077</v>
       </c>
       <c r="N30">
-        <v>51.85339026666667</v>
+        <v>51.36005896666667</v>
       </c>
       <c r="O30">
-        <v>7.77800854</v>
+        <v>7.704008845000001</v>
       </c>
       <c r="P30">
-        <v>44.07538172666667</v>
+        <v>43.65605012166667</v>
       </c>
       <c r="Q30">
-        <v>73.07538172666668</v>
+        <v>72.65605012166667</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1035987860517015</v>
+        <v>0.1043210796819751</v>
       </c>
       <c r="T30">
-        <v>1.096421613427978</v>
+        <v>1.110123256690258</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.753880597558061</v>
+        <v>4.589953680400887</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0876994165742023</v>
+        <v>0.08828380719117951</v>
       </c>
       <c r="C31">
-        <v>710.9506286408937</v>
+        <v>688.9045823952274</v>
       </c>
       <c r="D31">
-        <v>954.1596286408936</v>
+        <v>941.0345823952274</v>
       </c>
       <c r="E31">
-        <v>-444.091</v>
+        <v>-435.17</v>
       </c>
       <c r="F31">
-        <v>258.7089999999999</v>
+        <v>267.6299999999999</v>
       </c>
       <c r="G31">
         <v>15.5</v>
@@ -3829,45 +3829,45 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M31">
-        <v>14.3066077</v>
+        <v>15.469014</v>
       </c>
       <c r="N31">
-        <v>51.36005896666667</v>
+        <v>50.19765266666667</v>
       </c>
       <c r="O31">
-        <v>7.704008845000001</v>
+        <v>7.529647900000001</v>
       </c>
       <c r="P31">
-        <v>43.65605012166667</v>
+        <v>42.66800476666667</v>
       </c>
       <c r="Q31">
-        <v>72.65605012166667</v>
+        <v>71.66800476666667</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1043210796819751</v>
+        <v>0.1050640102731136</v>
       </c>
       <c r="T31">
-        <v>1.110123256690258</v>
+        <v>1.124216375474318</v>
       </c>
       <c r="U31">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V31">
         <v>0.15</v>
       </c>
       <c r="W31">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y31">
-        <v>4.589953680400888</v>
+        <v>4.245045396343082</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08828380719117951</v>
+        <v>0.08825194780815671</v>
       </c>
       <c r="C32">
-        <v>688.9045823952274</v>
+        <v>680.6898110312779</v>
       </c>
       <c r="D32">
-        <v>941.0345823952274</v>
+        <v>941.7408110312779</v>
       </c>
       <c r="E32">
-        <v>-435.17</v>
+        <v>-426.249</v>
       </c>
       <c r="F32">
-        <v>267.6299999999999</v>
+        <v>276.551</v>
       </c>
       <c r="G32">
         <v>15.5</v>
@@ -3911,28 +3911,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M32">
-        <v>15.469014</v>
+        <v>15.9846478</v>
       </c>
       <c r="N32">
-        <v>50.19765266666667</v>
+        <v>49.68201886666667</v>
       </c>
       <c r="O32">
-        <v>7.529647900000001</v>
+        <v>7.45230283</v>
       </c>
       <c r="P32">
-        <v>42.66800476666667</v>
+        <v>42.22971603666667</v>
       </c>
       <c r="Q32">
-        <v>71.66800476666667</v>
+        <v>71.22971603666667</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1050640102731136</v>
+        <v>0.1058284750842851</v>
       </c>
       <c r="T32">
-        <v>1.124216375474318</v>
+        <v>1.138717990455017</v>
       </c>
       <c r="U32">
         <v>0.0578</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.245045396343082</v>
+        <v>4.108108448073949</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08825194780815671</v>
+        <v>0.08917208842513391</v>
       </c>
       <c r="C33">
-        <v>680.6898110312779</v>
+        <v>651.7897414877236</v>
       </c>
       <c r="D33">
-        <v>941.7408110312779</v>
+        <v>921.7617414877236</v>
       </c>
       <c r="E33">
-        <v>-426.249</v>
+        <v>-417.328</v>
       </c>
       <c r="F33">
-        <v>276.551</v>
+        <v>285.472</v>
       </c>
       <c r="G33">
         <v>15.5</v>
@@ -3993,45 +3993,45 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M33">
-        <v>15.9846478</v>
+        <v>17.4994336</v>
       </c>
       <c r="N33">
-        <v>49.68201886666667</v>
+        <v>48.16723306666667</v>
       </c>
       <c r="O33">
-        <v>7.45230283</v>
+        <v>7.22508496</v>
       </c>
       <c r="P33">
-        <v>42.22971603666667</v>
+        <v>40.94214810666666</v>
       </c>
       <c r="Q33">
-        <v>71.22971603666667</v>
+        <v>69.94214810666666</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1058284750842851</v>
+        <v>0.1066154241546087</v>
       </c>
       <c r="T33">
-        <v>1.138717990455017</v>
+        <v>1.153646123523384</v>
       </c>
       <c r="U33">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V33">
         <v>0.15</v>
       </c>
       <c r="W33">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.108108448073949</v>
+        <v>3.752502404801643</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08917208842513391</v>
+        <v>0.0891699790421111</v>
       </c>
       <c r="C34">
-        <v>651.7897414877236</v>
+        <v>642.913573157268</v>
       </c>
       <c r="D34">
-        <v>921.7617414877236</v>
+        <v>921.8065731572681</v>
       </c>
       <c r="E34">
-        <v>-417.328</v>
+        <v>-408.407</v>
       </c>
       <c r="F34">
-        <v>285.472</v>
+        <v>294.393</v>
       </c>
       <c r="G34">
         <v>15.5</v>
@@ -4075,28 +4075,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M34">
-        <v>17.4994336</v>
+        <v>18.0462909</v>
       </c>
       <c r="N34">
-        <v>48.16723306666667</v>
+        <v>47.62037576666667</v>
       </c>
       <c r="O34">
-        <v>7.22508496</v>
+        <v>7.143056365000001</v>
       </c>
       <c r="P34">
-        <v>40.94214810666666</v>
+        <v>40.47731940166667</v>
       </c>
       <c r="Q34">
-        <v>69.94214810666666</v>
+        <v>69.47731940166668</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1066154241546087</v>
+        <v>0.1074258642419569</v>
       </c>
       <c r="T34">
-        <v>1.153646123523384</v>
+        <v>1.169019872504239</v>
       </c>
       <c r="U34">
         <v>0.0613</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.752502404801643</v>
+        <v>3.638790210716745</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0891699790421111</v>
+        <v>0.08916786965908832</v>
       </c>
       <c r="C35">
-        <v>642.913573157268</v>
+        <v>634.0374091879744</v>
       </c>
       <c r="D35">
-        <v>921.8065731572681</v>
+        <v>921.8514091879744</v>
       </c>
       <c r="E35">
-        <v>-408.407</v>
+        <v>-399.486</v>
       </c>
       <c r="F35">
-        <v>294.393</v>
+        <v>303.314</v>
       </c>
       <c r="G35">
         <v>15.5</v>
@@ -4157,28 +4157,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M35">
-        <v>18.0462909</v>
+        <v>18.5931482</v>
       </c>
       <c r="N35">
-        <v>47.62037576666667</v>
+        <v>47.07351846666667</v>
       </c>
       <c r="O35">
-        <v>7.143056365000001</v>
+        <v>7.06102777</v>
       </c>
       <c r="P35">
-        <v>40.47731940166667</v>
+        <v>40.01249069666667</v>
       </c>
       <c r="Q35">
-        <v>69.47731940166668</v>
+        <v>69.01249069666667</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1074258642419569</v>
+        <v>0.1082608631198308</v>
       </c>
       <c r="T35">
-        <v>1.169019872504239</v>
+        <v>1.184859492666333</v>
       </c>
       <c r="U35">
         <v>0.0613</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.638790210716745</v>
+        <v>3.531766969225076</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08916786965908832</v>
+        <v>0.08999876027606553</v>
       </c>
       <c r="C36">
-        <v>634.0374091879744</v>
+        <v>607.7865637045869</v>
       </c>
       <c r="D36">
-        <v>921.8514091879744</v>
+        <v>904.5215637045869</v>
       </c>
       <c r="E36">
-        <v>-399.486</v>
+        <v>-390.5649999999999</v>
       </c>
       <c r="F36">
-        <v>303.314</v>
+        <v>312.235</v>
       </c>
       <c r="G36">
         <v>15.5</v>
@@ -4239,45 +4239,45 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M36">
-        <v>18.5931482</v>
+        <v>20.0142635</v>
       </c>
       <c r="N36">
-        <v>47.07351846666667</v>
+        <v>45.65240316666667</v>
       </c>
       <c r="O36">
-        <v>7.06102777</v>
+        <v>6.847860475000001</v>
       </c>
       <c r="P36">
-        <v>40.01249069666667</v>
+        <v>38.80454269166667</v>
       </c>
       <c r="Q36">
-        <v>69.01249069666667</v>
+        <v>67.80454269166667</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1082608631198308</v>
+        <v>0.1091215542708701</v>
       </c>
       <c r="T36">
-        <v>1.184859492666333</v>
+        <v>1.20118648575649</v>
       </c>
       <c r="U36">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V36">
         <v>0.15</v>
       </c>
       <c r="W36">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.531766969225076</v>
+        <v>3.280993410857545</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08999876027606553</v>
+        <v>0.09002045089304272</v>
       </c>
       <c r="C37">
-        <v>607.7865637045869</v>
+        <v>598.4218859403463</v>
       </c>
       <c r="D37">
-        <v>904.5215637045869</v>
+        <v>904.0778859403463</v>
       </c>
       <c r="E37">
-        <v>-390.5649999999999</v>
+        <v>-381.6439999999999</v>
       </c>
       <c r="F37">
-        <v>312.235</v>
+        <v>321.156</v>
       </c>
       <c r="G37">
         <v>15.5</v>
@@ -4321,28 +4321,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M37">
-        <v>20.0142635</v>
+        <v>20.5860996</v>
       </c>
       <c r="N37">
-        <v>45.65240316666667</v>
+        <v>45.08056706666667</v>
       </c>
       <c r="O37">
-        <v>6.847860475000001</v>
+        <v>6.762085060000001</v>
       </c>
       <c r="P37">
-        <v>38.80454269166667</v>
+        <v>38.31848200666667</v>
       </c>
       <c r="Q37">
-        <v>67.80454269166667</v>
+        <v>67.31848200666667</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1091215542708701</v>
+        <v>0.1100091420203793</v>
       </c>
       <c r="T37">
-        <v>1.20118648575649</v>
+        <v>1.218023697380715</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.280993410857545</v>
+        <v>3.189854705000391</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09002045089304272</v>
+        <v>0.09004214151001995</v>
       </c>
       <c r="C38">
-        <v>598.4218859403463</v>
+        <v>589.0576432203468</v>
       </c>
       <c r="D38">
-        <v>904.0778859403463</v>
+        <v>903.6346432203467</v>
       </c>
       <c r="E38">
-        <v>-381.644</v>
+        <v>-372.723</v>
       </c>
       <c r="F38">
-        <v>321.1559999999999</v>
+        <v>330.0769999999999</v>
       </c>
       <c r="G38">
         <v>15.5</v>
@@ -4403,28 +4403,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M38">
-        <v>20.5860996</v>
+        <v>21.1579357</v>
       </c>
       <c r="N38">
-        <v>45.08056706666667</v>
+        <v>44.50873096666668</v>
       </c>
       <c r="O38">
-        <v>6.762085060000001</v>
+        <v>6.676309645000001</v>
       </c>
       <c r="P38">
-        <v>38.31848200666667</v>
+        <v>37.83242132166667</v>
       </c>
       <c r="Q38">
-        <v>67.31848200666667</v>
+        <v>66.83242132166667</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1100091420203793</v>
+        <v>0.1109249071587618</v>
       </c>
       <c r="T38">
-        <v>1.218023697380715</v>
+        <v>1.235395423659678</v>
       </c>
       <c r="U38">
         <v>0.0641</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.189854705000392</v>
+        <v>3.103642415676057</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09004214151001995</v>
+        <v>0.09006383212699715</v>
       </c>
       <c r="C39">
-        <v>589.0576432203468</v>
+        <v>579.6938349050347</v>
       </c>
       <c r="D39">
-        <v>903.6346432203467</v>
+        <v>903.1918349050346</v>
       </c>
       <c r="E39">
-        <v>-372.723</v>
+        <v>-363.802</v>
       </c>
       <c r="F39">
-        <v>330.0769999999999</v>
+        <v>338.998</v>
       </c>
       <c r="G39">
         <v>15.5</v>
@@ -4485,28 +4485,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M39">
-        <v>21.1579357</v>
+        <v>21.7297718</v>
       </c>
       <c r="N39">
-        <v>44.50873096666668</v>
+        <v>43.93689486666667</v>
       </c>
       <c r="O39">
-        <v>6.676309645000001</v>
+        <v>6.59053423</v>
       </c>
       <c r="P39">
-        <v>37.83242132166667</v>
+        <v>37.34636063666667</v>
       </c>
       <c r="Q39">
-        <v>66.83242132166667</v>
+        <v>66.34636063666667</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1109249071587618</v>
+        <v>0.1118702131080599</v>
       </c>
       <c r="T39">
-        <v>1.235395423659678</v>
+        <v>1.253327528205704</v>
       </c>
       <c r="U39">
         <v>0.0641</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.103642415676057</v>
+        <v>3.021967615263528</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09006383212699715</v>
+        <v>0.09267122274397435</v>
       </c>
       <c r="C40">
-        <v>579.6938349050347</v>
+        <v>520.5293426768621</v>
       </c>
       <c r="D40">
-        <v>903.1918349050346</v>
+        <v>852.9483426768621</v>
       </c>
       <c r="E40">
-        <v>-363.802</v>
+        <v>-354.881</v>
       </c>
       <c r="F40">
-        <v>338.998</v>
+        <v>347.919</v>
       </c>
       <c r="G40">
         <v>15.5</v>
@@ -4567,45 +4567,45 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M40">
-        <v>21.7297718</v>
+        <v>25.0153761</v>
       </c>
       <c r="N40">
-        <v>43.93689486666667</v>
+        <v>40.65129056666667</v>
       </c>
       <c r="O40">
-        <v>6.59053423</v>
+        <v>6.097693585000001</v>
       </c>
       <c r="P40">
-        <v>37.34636063666667</v>
+        <v>34.55359698166667</v>
       </c>
       <c r="Q40">
-        <v>66.34636063666667</v>
+        <v>63.55359698166667</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1118702131080599</v>
+        <v>0.1128465126950399</v>
       </c>
       <c r="T40">
-        <v>1.253327528205704</v>
+        <v>1.271847570605698</v>
       </c>
       <c r="U40">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V40">
         <v>0.15</v>
       </c>
       <c r="W40">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.021967615263528</v>
+        <v>2.625052144095754</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09267122274397435</v>
+        <v>0.09275921336095155</v>
       </c>
       <c r="C41">
-        <v>520.5293426768621</v>
+        <v>510.0101163534155</v>
       </c>
       <c r="D41">
-        <v>852.9483426768621</v>
+        <v>851.3501163534155</v>
       </c>
       <c r="E41">
-        <v>-354.881</v>
+        <v>-345.96</v>
       </c>
       <c r="F41">
-        <v>347.919</v>
+        <v>356.84</v>
       </c>
       <c r="G41">
         <v>15.5</v>
@@ -4649,28 +4649,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M41">
-        <v>25.0153761</v>
+        <v>25.656796</v>
       </c>
       <c r="N41">
-        <v>40.65129056666667</v>
+        <v>40.00987066666667</v>
       </c>
       <c r="O41">
-        <v>6.097693585000001</v>
+        <v>6.001480600000001</v>
       </c>
       <c r="P41">
-        <v>34.55359698166667</v>
+        <v>34.00839006666667</v>
       </c>
       <c r="Q41">
-        <v>63.55359698166667</v>
+        <v>63.00839006666667</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1128465126950399</v>
+        <v>0.1138553556015859</v>
       </c>
       <c r="T41">
-        <v>1.271847570605698</v>
+        <v>1.290984947752358</v>
       </c>
       <c r="U41">
         <v>0.07190000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.625052144095754</v>
+        <v>2.55942584049336</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09275921336095155</v>
+        <v>0.09420635397792876</v>
       </c>
       <c r="C42">
-        <v>510.0101163534155</v>
+        <v>475.6374301304654</v>
       </c>
       <c r="D42">
-        <v>851.3501163534155</v>
+        <v>825.8984301304654</v>
       </c>
       <c r="E42">
-        <v>-345.96</v>
+        <v>-337.039</v>
       </c>
       <c r="F42">
-        <v>356.84</v>
+        <v>365.761</v>
       </c>
       <c r="G42">
         <v>15.5</v>
@@ -4731,45 +4731,45 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M42">
-        <v>25.656796</v>
+        <v>27.7246838</v>
       </c>
       <c r="N42">
-        <v>40.00987066666667</v>
+        <v>37.94198286666667</v>
       </c>
       <c r="O42">
-        <v>6.001480600000001</v>
+        <v>5.691297430000001</v>
       </c>
       <c r="P42">
-        <v>34.00839006666667</v>
+        <v>32.25068543666667</v>
       </c>
       <c r="Q42">
-        <v>63.00839006666667</v>
+        <v>61.25068543666667</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1138553556015859</v>
+        <v>0.1148983965727606</v>
       </c>
       <c r="T42">
-        <v>1.290984947752358</v>
+        <v>1.310771049548058</v>
       </c>
       <c r="U42">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V42">
         <v>0.15</v>
       </c>
       <c r="W42">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.55942584049336</v>
+        <v>2.368527163028156</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09420635397792876</v>
+        <v>0.09432749459490597</v>
       </c>
       <c r="C43">
-        <v>475.6374301304654</v>
+        <v>464.6547155041138</v>
       </c>
       <c r="D43">
-        <v>825.8984301304654</v>
+        <v>823.8367155041138</v>
       </c>
       <c r="E43">
-        <v>-337.039</v>
+        <v>-328.1179999999999</v>
       </c>
       <c r="F43">
-        <v>365.761</v>
+        <v>374.682</v>
       </c>
       <c r="G43">
         <v>15.5</v>
@@ -4813,28 +4813,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M43">
-        <v>27.7246838</v>
+        <v>28.4008956</v>
       </c>
       <c r="N43">
-        <v>37.94198286666667</v>
+        <v>37.26577106666667</v>
       </c>
       <c r="O43">
-        <v>5.691297430000001</v>
+        <v>5.589865660000001</v>
       </c>
       <c r="P43">
-        <v>32.25068543666667</v>
+        <v>31.67590540666667</v>
       </c>
       <c r="Q43">
-        <v>61.25068543666667</v>
+        <v>60.67590540666667</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1148983965727606</v>
+        <v>0.1159774044739758</v>
       </c>
       <c r="T43">
-        <v>1.310771049548058</v>
+        <v>1.331239430716023</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.368527163028156</v>
+        <v>2.312133659146533</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09432749459490597</v>
+        <v>0.09444863521188318</v>
       </c>
       <c r="C44">
-        <v>464.6547155041139</v>
+        <v>453.682268684075</v>
       </c>
       <c r="D44">
-        <v>823.8367155041138</v>
+        <v>821.7852686840749</v>
       </c>
       <c r="E44">
-        <v>-328.118</v>
+        <v>-319.197</v>
       </c>
       <c r="F44">
-        <v>374.682</v>
+        <v>383.603</v>
       </c>
       <c r="G44">
         <v>15.5</v>
@@ -4895,28 +4895,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M44">
-        <v>28.4008956</v>
+        <v>29.0771074</v>
       </c>
       <c r="N44">
-        <v>37.26577106666667</v>
+        <v>36.58955926666667</v>
       </c>
       <c r="O44">
-        <v>5.589865660000001</v>
+        <v>5.48843389</v>
       </c>
       <c r="P44">
-        <v>31.67590540666667</v>
+        <v>31.10112537666667</v>
       </c>
       <c r="Q44">
-        <v>60.67590540666667</v>
+        <v>60.10112537666667</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1159774044739758</v>
+        <v>0.1170942723015494</v>
       </c>
       <c r="T44">
-        <v>1.331239430716023</v>
+        <v>1.352426000696899</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.312133659146533</v>
+        <v>2.258363108933823</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09444863521188318</v>
+        <v>0.09456977582886038</v>
       </c>
       <c r="C45">
-        <v>453.682268684075</v>
+        <v>442.7200131568711</v>
       </c>
       <c r="D45">
-        <v>821.7852686840749</v>
+        <v>819.744013156871</v>
       </c>
       <c r="E45">
-        <v>-319.197</v>
+        <v>-310.276</v>
       </c>
       <c r="F45">
-        <v>383.603</v>
+        <v>392.5239999999999</v>
       </c>
       <c r="G45">
         <v>15.5</v>
@@ -4977,28 +4977,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M45">
-        <v>29.0771074</v>
+        <v>29.7533192</v>
       </c>
       <c r="N45">
-        <v>36.58955926666667</v>
+        <v>35.91334746666667</v>
       </c>
       <c r="O45">
-        <v>5.48843389</v>
+        <v>5.387002120000001</v>
       </c>
       <c r="P45">
-        <v>31.10112537666667</v>
+        <v>30.52634534666667</v>
       </c>
       <c r="Q45">
-        <v>60.10112537666667</v>
+        <v>59.52634534666667</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1170942723015494</v>
+        <v>0.1182510282658221</v>
       </c>
       <c r="T45">
-        <v>1.352426000696899</v>
+        <v>1.374369233891378</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.258363108933823</v>
+        <v>2.207036674639872</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09456977582886038</v>
+        <v>0.09469091644583759</v>
       </c>
       <c r="C46">
-        <v>442.7200131568711</v>
+        <v>431.7678731673555</v>
       </c>
       <c r="D46">
-        <v>819.744013156871</v>
+        <v>817.7128731673555</v>
       </c>
       <c r="E46">
-        <v>-310.276</v>
+        <v>-301.355</v>
       </c>
       <c r="F46">
-        <v>392.5239999999999</v>
+        <v>401.445</v>
       </c>
       <c r="G46">
         <v>15.5</v>
@@ -5059,28 +5059,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M46">
-        <v>29.7533192</v>
+        <v>30.429531</v>
       </c>
       <c r="N46">
-        <v>35.91334746666667</v>
+        <v>35.23713566666667</v>
       </c>
       <c r="O46">
-        <v>5.387002120000001</v>
+        <v>5.285570350000001</v>
       </c>
       <c r="P46">
-        <v>30.52634534666667</v>
+        <v>29.95156531666667</v>
       </c>
       <c r="Q46">
-        <v>59.52634534666667</v>
+        <v>58.95156531666667</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1182510282658221</v>
+        <v>0.1194498480833411</v>
       </c>
       <c r="T46">
-        <v>1.374369233891378</v>
+        <v>1.397110402838383</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.207036674639872</v>
+        <v>2.157991415203431</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09469091644583759</v>
+        <v>0.0948120570628148</v>
       </c>
       <c r="C47">
-        <v>431.7678731673555</v>
+        <v>420.8257737093437</v>
       </c>
       <c r="D47">
-        <v>817.7128731673555</v>
+        <v>815.6917737093437</v>
       </c>
       <c r="E47">
-        <v>-301.355</v>
+        <v>-292.434</v>
       </c>
       <c r="F47">
-        <v>401.445</v>
+        <v>410.366</v>
       </c>
       <c r="G47">
         <v>15.5</v>
@@ -5141,28 +5141,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M47">
-        <v>30.429531</v>
+        <v>31.1057428</v>
       </c>
       <c r="N47">
-        <v>35.23713566666667</v>
+        <v>34.56092386666667</v>
       </c>
       <c r="O47">
-        <v>5.285570350000001</v>
+        <v>5.18413858</v>
       </c>
       <c r="P47">
-        <v>29.95156531666667</v>
+        <v>29.37678528666667</v>
       </c>
       <c r="Q47">
-        <v>58.95156531666667</v>
+        <v>58.37678528666667</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1194498480833411</v>
+        <v>0.1206930686348422</v>
       </c>
       <c r="T47">
-        <v>1.397110402838383</v>
+        <v>1.420693837301945</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.157991415203431</v>
+        <v>2.111078558351182</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.0948120570628148</v>
+        <v>0.094933197679792</v>
       </c>
       <c r="C48">
-        <v>420.8257737093437</v>
+        <v>409.8936405163781</v>
       </c>
       <c r="D48">
-        <v>815.6917737093437</v>
+        <v>813.680640516378</v>
       </c>
       <c r="E48">
-        <v>-292.434</v>
+        <v>-283.513</v>
       </c>
       <c r="F48">
-        <v>410.366</v>
+        <v>419.287</v>
       </c>
       <c r="G48">
         <v>15.5</v>
@@ -5223,28 +5223,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M48">
-        <v>31.1057428</v>
+        <v>31.7819546</v>
       </c>
       <c r="N48">
-        <v>34.56092386666667</v>
+        <v>33.88471206666667</v>
       </c>
       <c r="O48">
-        <v>5.18413858</v>
+        <v>5.082706809999999</v>
       </c>
       <c r="P48">
-        <v>29.37678528666667</v>
+        <v>28.80200525666667</v>
       </c>
       <c r="Q48">
-        <v>58.37678528666667</v>
+        <v>57.80200525666667</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1206930686348422</v>
+        <v>0.1219832031694189</v>
       </c>
       <c r="T48">
-        <v>1.420693837301945</v>
+        <v>1.445167212688659</v>
       </c>
       <c r="U48">
         <v>0.07580000000000001</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.111078558351182</v>
+        <v>2.06616199327988</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.094933197679792</v>
+        <v>0.09505433829676919</v>
       </c>
       <c r="C49">
-        <v>409.8936405163781</v>
+        <v>398.9714000526315</v>
       </c>
       <c r="D49">
-        <v>813.680640516378</v>
+        <v>811.6794000526314</v>
       </c>
       <c r="E49">
-        <v>-283.513</v>
+        <v>-274.592</v>
       </c>
       <c r="F49">
-        <v>419.287</v>
+        <v>428.208</v>
       </c>
       <c r="G49">
         <v>15.5</v>
@@ -5305,28 +5305,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M49">
-        <v>31.7819546</v>
+        <v>32.4581664</v>
       </c>
       <c r="N49">
-        <v>33.88471206666667</v>
+        <v>33.20850026666667</v>
       </c>
       <c r="O49">
-        <v>5.082706809999999</v>
+        <v>4.98127504</v>
       </c>
       <c r="P49">
-        <v>28.80200525666667</v>
+        <v>28.22722522666667</v>
       </c>
       <c r="Q49">
-        <v>57.80200525666667</v>
+        <v>57.22722522666667</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1219832031694189</v>
+        <v>0.1233229582630177</v>
       </c>
       <c r="T49">
-        <v>1.445167212688659</v>
+        <v>1.470581871744093</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.06616199327988</v>
+        <v>2.023116951753216</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09505433829676918</v>
+        <v>0.1010897789137464</v>
       </c>
       <c r="C50">
-        <v>398.9714000526319</v>
+        <v>301.4473541499942</v>
       </c>
       <c r="D50">
-        <v>811.6794000526318</v>
+        <v>723.0763541499941</v>
       </c>
       <c r="E50">
-        <v>-274.592</v>
+        <v>-265.671</v>
       </c>
       <c r="F50">
-        <v>428.2079999999999</v>
+        <v>437.129</v>
       </c>
       <c r="G50">
         <v>15.5</v>
@@ -5387,45 +5387,45 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M50">
-        <v>32.4581664</v>
+        <v>39.34161</v>
       </c>
       <c r="N50">
-        <v>33.20850026666668</v>
+        <v>26.32505666666668</v>
       </c>
       <c r="O50">
-        <v>4.981275040000001</v>
+        <v>3.948758500000001</v>
       </c>
       <c r="P50">
-        <v>28.22722522666668</v>
+        <v>22.37629816666668</v>
       </c>
       <c r="Q50">
-        <v>57.22722522666668</v>
+        <v>51.37629816666667</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1233229582630177</v>
+        <v>0.1247152527720518</v>
       </c>
       <c r="T50">
-        <v>1.470581871744093</v>
+        <v>1.496993184095819</v>
       </c>
       <c r="U50">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V50">
         <v>0.15</v>
       </c>
       <c r="W50">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>2.023116951753217</v>
+        <v>1.669140298698164</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1010897789137464</v>
+        <v>0.1013316195307236</v>
       </c>
       <c r="C51">
-        <v>301.4473541499942</v>
+        <v>289.3773512380131</v>
       </c>
       <c r="D51">
-        <v>723.0763541499941</v>
+        <v>719.9273512380131</v>
       </c>
       <c r="E51">
-        <v>-265.671</v>
+        <v>-256.75</v>
       </c>
       <c r="F51">
-        <v>437.129</v>
+        <v>446.05</v>
       </c>
       <c r="G51">
         <v>15.5</v>
@@ -5469,28 +5469,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M51">
-        <v>39.34161</v>
+        <v>40.14449999999999</v>
       </c>
       <c r="N51">
-        <v>26.32505666666668</v>
+        <v>25.52216666666668</v>
       </c>
       <c r="O51">
-        <v>3.948758500000001</v>
+        <v>3.828325000000001</v>
       </c>
       <c r="P51">
-        <v>22.37629816666668</v>
+        <v>21.69384166666668</v>
       </c>
       <c r="Q51">
-        <v>51.37629816666667</v>
+        <v>50.69384166666668</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1247152527720518</v>
+        <v>0.1261632390614472</v>
       </c>
       <c r="T51">
-        <v>1.496993184095819</v>
+        <v>1.524460948941614</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.669140298698164</v>
+        <v>1.635757492724201</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1013316195307236</v>
+        <v>0.1015734601477008</v>
       </c>
       <c r="C52">
-        <v>289.3773512380131</v>
+        <v>277.3346572577388</v>
       </c>
       <c r="D52">
-        <v>719.9273512380131</v>
+        <v>716.8056572577387</v>
       </c>
       <c r="E52">
-        <v>-256.75</v>
+        <v>-247.829</v>
       </c>
       <c r="F52">
-        <v>446.05</v>
+        <v>454.9709999999999</v>
       </c>
       <c r="G52">
         <v>15.5</v>
@@ -5551,28 +5551,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M52">
-        <v>40.14449999999999</v>
+        <v>40.94738999999999</v>
       </c>
       <c r="N52">
-        <v>25.52216666666668</v>
+        <v>24.71927666666668</v>
       </c>
       <c r="O52">
-        <v>3.828325000000001</v>
+        <v>3.707891500000002</v>
       </c>
       <c r="P52">
-        <v>21.69384166666668</v>
+        <v>21.01138516666668</v>
       </c>
       <c r="Q52">
-        <v>50.69384166666668</v>
+        <v>50.01138516666668</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1261632390614472</v>
+        <v>0.1276703268320425</v>
       </c>
       <c r="T52">
-        <v>1.524460948941614</v>
+        <v>1.553049847046421</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.635757492724201</v>
+        <v>1.603683816396275</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1015734601477008</v>
+        <v>0.101815300764678</v>
       </c>
       <c r="C53">
-        <v>277.3346572577388</v>
+        <v>265.3189184981946</v>
       </c>
       <c r="D53">
-        <v>716.8056572577387</v>
+        <v>713.7109184981946</v>
       </c>
       <c r="E53">
-        <v>-247.829</v>
+        <v>-238.908</v>
       </c>
       <c r="F53">
-        <v>454.9709999999999</v>
+        <v>463.892</v>
       </c>
       <c r="G53">
         <v>15.5</v>
@@ -5633,28 +5633,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M53">
-        <v>40.94738999999999</v>
+        <v>41.75028</v>
       </c>
       <c r="N53">
-        <v>24.71927666666668</v>
+        <v>23.91638666666667</v>
       </c>
       <c r="O53">
-        <v>3.707891500000002</v>
+        <v>3.587458000000001</v>
       </c>
       <c r="P53">
-        <v>21.01138516666668</v>
+        <v>20.32892866666667</v>
       </c>
       <c r="Q53">
-        <v>50.01138516666668</v>
+        <v>49.32892866666667</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1276703268320425</v>
+        <v>0.1292402099264125</v>
       </c>
       <c r="T53">
-        <v>1.553049847046421</v>
+        <v>1.582829949238928</v>
       </c>
       <c r="U53">
         <v>0.09</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>1.603683816396275</v>
+        <v>1.572843743004039</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.101815300764678</v>
+        <v>0.1020571413816552</v>
       </c>
       <c r="C54">
-        <v>265.3189184981946</v>
+        <v>253.3297873305976</v>
       </c>
       <c r="D54">
-        <v>713.7109184981946</v>
+        <v>710.6427873305976</v>
       </c>
       <c r="E54">
-        <v>-238.908</v>
+        <v>-229.987</v>
       </c>
       <c r="F54">
-        <v>463.892</v>
+        <v>472.813</v>
       </c>
       <c r="G54">
         <v>15.5</v>
@@ -5715,28 +5715,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M54">
-        <v>41.75028</v>
+        <v>42.55316999999999</v>
       </c>
       <c r="N54">
-        <v>23.91638666666667</v>
+        <v>23.11349666666668</v>
       </c>
       <c r="O54">
-        <v>3.587458000000001</v>
+        <v>3.467024500000001</v>
       </c>
       <c r="P54">
-        <v>20.32892866666667</v>
+        <v>19.64647216666668</v>
       </c>
       <c r="Q54">
-        <v>49.32892866666667</v>
+        <v>48.64647216666668</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1292402099264125</v>
+        <v>0.1308768965567132</v>
       </c>
       <c r="T54">
-        <v>1.582829949238928</v>
+        <v>1.613877289822606</v>
       </c>
       <c r="U54">
         <v>0.09</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>1.572843743004039</v>
+        <v>1.543167445966227</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1020571413816552</v>
+        <v>0.1022989819986324</v>
       </c>
       <c r="C55">
-        <v>253.3297873305976</v>
+        <v>241.3669220781833</v>
       </c>
       <c r="D55">
-        <v>710.6427873305976</v>
+        <v>707.6009220781833</v>
       </c>
       <c r="E55">
-        <v>-229.987</v>
+        <v>-221.066</v>
       </c>
       <c r="F55">
-        <v>472.813</v>
+        <v>481.734</v>
       </c>
       <c r="G55">
         <v>15.5</v>
@@ -5797,28 +5797,28 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M55">
-        <v>42.55316999999999</v>
+        <v>43.35606</v>
       </c>
       <c r="N55">
-        <v>23.11349666666668</v>
+        <v>22.31060666666667</v>
       </c>
       <c r="O55">
-        <v>3.467024500000001</v>
+        <v>3.346591000000001</v>
       </c>
       <c r="P55">
-        <v>19.64647216666668</v>
+        <v>18.96401566666667</v>
       </c>
       <c r="Q55">
-        <v>48.64647216666668</v>
+        <v>47.96401566666667</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1308768965567132</v>
+        <v>0.1325847434752879</v>
       </c>
       <c r="T55">
-        <v>1.613877289822606</v>
+        <v>1.646274514779487</v>
       </c>
       <c r="U55">
         <v>0.09</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>1.543167445966227</v>
+        <v>1.514590271040926</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1022989819986324</v>
+        <v>0.1304809758069035</v>
       </c>
       <c r="C56">
-        <v>241.3669220781833</v>
+        <v>-3.045044041606786</v>
       </c>
       <c r="D56">
-        <v>707.6009220781833</v>
+        <v>472.1099559583932</v>
       </c>
       <c r="E56">
-        <v>-221.066</v>
+        <v>-212.145</v>
       </c>
       <c r="F56">
-        <v>481.734</v>
+        <v>490.655</v>
       </c>
       <c r="G56">
         <v>15.5</v>
@@ -5879,45 +5879,45 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M56">
-        <v>43.35606</v>
+        <v>72.028154</v>
       </c>
       <c r="N56">
-        <v>22.31060666666667</v>
+        <v>-6.361487333333329</v>
       </c>
       <c r="O56">
-        <v>3.346591000000001</v>
+        <v>-0.9542230999999993</v>
       </c>
       <c r="P56">
-        <v>18.96401566666667</v>
+        <v>-5.40726423333333</v>
       </c>
       <c r="Q56">
-        <v>47.96401566666667</v>
+        <v>23.59273576666667</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1325847434752879</v>
+        <v>0.1350718641839818</v>
       </c>
       <c r="T56">
-        <v>1.646274514779487</v>
+        <v>1.69345427557545</v>
       </c>
       <c r="U56">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.15</v>
+        <v>0.1367520816929447</v>
       </c>
       <c r="W56">
-        <v>0.0765</v>
+        <v>0.1267247944074757</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y56">
-        <v>1.514590271040926</v>
+        <v>0.9116805446196312</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1304809758069035</v>
+        <v>0.1314909758069035</v>
       </c>
       <c r="C57">
-        <v>-3.045044041606786</v>
+        <v>-17.53058629390262</v>
       </c>
       <c r="D57">
-        <v>472.1099559583932</v>
+        <v>466.5454137060974</v>
       </c>
       <c r="E57">
-        <v>-212.145</v>
+        <v>-203.2239999999999</v>
       </c>
       <c r="F57">
-        <v>490.655</v>
+        <v>499.576</v>
       </c>
       <c r="G57">
         <v>15.5</v>
@@ -5961,37 +5961,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M57">
-        <v>72.028154</v>
+        <v>73.33775680000001</v>
       </c>
       <c r="N57">
-        <v>-6.361487333333329</v>
+        <v>-7.671090133333337</v>
       </c>
       <c r="O57">
-        <v>-0.9542230999999993</v>
+        <v>-1.15066352</v>
       </c>
       <c r="P57">
-        <v>-5.40726423333333</v>
+        <v>-6.520426613333337</v>
       </c>
       <c r="Q57">
-        <v>23.59273576666667</v>
+        <v>22.47957338666667</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1350718641839818</v>
+        <v>0.1371007701881632</v>
       </c>
       <c r="T57">
-        <v>1.69345427557545</v>
+        <v>1.731941872747619</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.1367520816929447</v>
+        <v>0.1343100802341421</v>
       </c>
       <c r="W57">
-        <v>0.1267247944074757</v>
+        <v>0.1270832802216279</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.9116805446196312</v>
+        <v>0.8954005348942806</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1314909758069035</v>
+        <v>0.1325009758069035</v>
       </c>
       <c r="C58">
-        <v>-17.53058629390262</v>
+        <v>-31.8864832308484</v>
       </c>
       <c r="D58">
-        <v>466.5454137060974</v>
+        <v>461.1105167691516</v>
       </c>
       <c r="E58">
-        <v>-203.2239999999999</v>
+        <v>-194.3029999999999</v>
       </c>
       <c r="F58">
-        <v>499.576</v>
+        <v>508.497</v>
       </c>
       <c r="G58">
         <v>15.5</v>
@@ -6043,37 +6043,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M58">
-        <v>73.33775680000001</v>
+        <v>74.64735960000002</v>
       </c>
       <c r="N58">
-        <v>-7.671090133333337</v>
+        <v>-8.980692933333344</v>
       </c>
       <c r="O58">
-        <v>-1.15066352</v>
+        <v>-1.347103940000002</v>
       </c>
       <c r="P58">
-        <v>-6.520426613333337</v>
+        <v>-7.633588993333342</v>
       </c>
       <c r="Q58">
-        <v>22.47957338666667</v>
+        <v>21.36641100666666</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1371007701881632</v>
+        <v>0.1392240439134693</v>
       </c>
       <c r="T58">
-        <v>1.731941872747619</v>
+        <v>1.772219590718495</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.1343100802341421</v>
+        <v>0.1319537630370519</v>
       </c>
       <c r="W58">
-        <v>0.1270832802216279</v>
+        <v>0.1274291875861608</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8954005348942806</v>
+        <v>0.8796917535803458</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1325009758069035</v>
+        <v>0.1335109758069035</v>
       </c>
       <c r="C59">
-        <v>-31.8864832308484</v>
+        <v>-46.11721348584098</v>
       </c>
       <c r="D59">
-        <v>461.1105167691516</v>
+        <v>455.800786514159</v>
       </c>
       <c r="E59">
-        <v>-194.3029999999999</v>
+        <v>-185.3819999999999</v>
       </c>
       <c r="F59">
-        <v>508.497</v>
+        <v>517.418</v>
       </c>
       <c r="G59">
         <v>15.5</v>
@@ -6125,37 +6125,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M59">
-        <v>74.64735960000002</v>
+        <v>75.95696240000001</v>
       </c>
       <c r="N59">
-        <v>-8.980692933333344</v>
+        <v>-10.29029573333334</v>
       </c>
       <c r="O59">
-        <v>-1.347103940000002</v>
+        <v>-1.543544360000001</v>
       </c>
       <c r="P59">
-        <v>-7.633588993333342</v>
+        <v>-8.746751373333337</v>
       </c>
       <c r="Q59">
-        <v>21.36641100666666</v>
+        <v>20.25324862666666</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1392240439134693</v>
+        <v>0.1414484259114091</v>
       </c>
       <c r="T59">
-        <v>1.772219590718495</v>
+        <v>1.814415295259411</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.1319537630370519</v>
+        <v>0.1296786981571027</v>
       </c>
       <c r="W59">
-        <v>0.1274291875861608</v>
+        <v>0.1277631671105373</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8796917535803458</v>
+        <v>0.8645246543806847</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1335109758069035</v>
+        <v>0.1345209758069035</v>
       </c>
       <c r="C60">
-        <v>-46.11721348584086</v>
+        <v>-60.22705175314377</v>
       </c>
       <c r="D60">
-        <v>455.800786514159</v>
+        <v>450.6119482468562</v>
       </c>
       <c r="E60">
-        <v>-185.3820000000001</v>
+        <v>-176.461</v>
       </c>
       <c r="F60">
-        <v>517.4179999999999</v>
+        <v>526.3389999999999</v>
       </c>
       <c r="G60">
         <v>15.5</v>
@@ -6207,37 +6207,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M60">
-        <v>75.95696239999999</v>
+        <v>77.2665652</v>
       </c>
       <c r="N60">
-        <v>-10.29029573333332</v>
+        <v>-11.59989853333333</v>
       </c>
       <c r="O60">
-        <v>-1.543544359999999</v>
+        <v>-1.73998478</v>
       </c>
       <c r="P60">
-        <v>-8.746751373333325</v>
+        <v>-9.859913753333331</v>
       </c>
       <c r="Q60">
-        <v>20.25324862666668</v>
+        <v>19.14008624666667</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.141448425911409</v>
+        <v>0.1437813143482727</v>
       </c>
       <c r="T60">
-        <v>1.81441529525941</v>
+        <v>1.858669326851104</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1296786981571027</v>
+        <v>0.1274807541205417</v>
       </c>
       <c r="W60">
-        <v>0.1277631671105373</v>
+        <v>0.1280858252951045</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8645246543806848</v>
+        <v>0.8498716941369444</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1345209758069035</v>
+        <v>0.1355309758069035</v>
       </c>
       <c r="C61">
-        <v>-60.22705175314377</v>
+        <v>-74.22008026544592</v>
       </c>
       <c r="D61">
-        <v>450.6119482468562</v>
+        <v>445.539919734554</v>
       </c>
       <c r="E61">
-        <v>-176.461</v>
+        <v>-167.5400000000001</v>
       </c>
       <c r="F61">
-        <v>526.3389999999999</v>
+        <v>535.2599999999999</v>
       </c>
       <c r="G61">
         <v>15.5</v>
@@ -6289,37 +6289,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M61">
-        <v>77.2665652</v>
+        <v>78.576168</v>
       </c>
       <c r="N61">
-        <v>-11.59989853333333</v>
+        <v>-12.90950133333332</v>
       </c>
       <c r="O61">
-        <v>-1.73998478</v>
+        <v>-1.936425199999999</v>
       </c>
       <c r="P61">
-        <v>-9.859913753333331</v>
+        <v>-10.97307613333333</v>
       </c>
       <c r="Q61">
-        <v>19.14008624666667</v>
+        <v>18.02692386666667</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1437813143482727</v>
+        <v>0.1462308472069795</v>
       </c>
       <c r="T61">
-        <v>1.858669326851104</v>
+        <v>1.905136060022381</v>
       </c>
       <c r="U61">
         <v>0.1468</v>
       </c>
       <c r="V61">
-        <v>0.1274807541205417</v>
+        <v>0.1253560748851993</v>
       </c>
       <c r="W61">
-        <v>0.1280858252951045</v>
+        <v>0.1283977282068527</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.8498716941369444</v>
+        <v>0.8357071659013287</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1355309758069035</v>
+        <v>0.1365409758069035</v>
       </c>
       <c r="C62">
-        <v>-74.22008026544592</v>
+        <v>-88.1001995049117</v>
       </c>
       <c r="D62">
-        <v>445.539919734554</v>
+        <v>440.5808004950882</v>
       </c>
       <c r="E62">
-        <v>-167.5400000000001</v>
+        <v>-158.619</v>
       </c>
       <c r="F62">
-        <v>535.2599999999999</v>
+        <v>544.1809999999999</v>
       </c>
       <c r="G62">
         <v>15.5</v>
@@ -6371,37 +6371,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M62">
-        <v>78.576168</v>
+        <v>79.8857708</v>
       </c>
       <c r="N62">
-        <v>-12.90950133333332</v>
+        <v>-14.21910413333333</v>
       </c>
       <c r="O62">
-        <v>-1.936425199999999</v>
+        <v>-2.13286562</v>
       </c>
       <c r="P62">
-        <v>-10.97307613333333</v>
+        <v>-12.08623851333333</v>
       </c>
       <c r="Q62">
-        <v>18.02692386666667</v>
+        <v>16.91376148666667</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1462308472069795</v>
+        <v>0.1488059971353636</v>
       </c>
       <c r="T62">
-        <v>1.905136060022381</v>
+        <v>1.953985702587058</v>
       </c>
       <c r="U62">
         <v>0.1468</v>
       </c>
       <c r="V62">
-        <v>0.1253560748851993</v>
+        <v>0.1233010572641304</v>
       </c>
       <c r="W62">
-        <v>0.1283977282068527</v>
+        <v>0.1286994047936257</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.8357071659013287</v>
+        <v>0.8220070484275364</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1365409758069035</v>
+        <v>0.1375509758069035</v>
       </c>
       <c r="C63">
-        <v>-88.1001995049117</v>
+        <v>-101.8711382067794</v>
       </c>
       <c r="D63">
-        <v>440.5808004950882</v>
+        <v>435.7308617932205</v>
       </c>
       <c r="E63">
-        <v>-158.619</v>
+        <v>-149.698</v>
       </c>
       <c r="F63">
-        <v>544.1809999999999</v>
+        <v>553.102</v>
       </c>
       <c r="G63">
         <v>15.5</v>
@@ -6453,37 +6453,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M63">
-        <v>79.8857708</v>
+        <v>81.19537360000001</v>
       </c>
       <c r="N63">
-        <v>-14.21910413333333</v>
+        <v>-15.52870693333334</v>
       </c>
       <c r="O63">
-        <v>-2.13286562</v>
+        <v>-2.329306040000001</v>
       </c>
       <c r="P63">
-        <v>-12.08623851333333</v>
+        <v>-13.19940089333334</v>
       </c>
       <c r="Q63">
-        <v>16.91376148666667</v>
+        <v>15.80059910666666</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1488059971353636</v>
+        <v>0.1515166812705047</v>
       </c>
       <c r="T63">
-        <v>1.953985702587058</v>
+        <v>2.005406378970927</v>
       </c>
       <c r="U63">
         <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.1233010572641304</v>
+        <v>0.1213123305340638</v>
       </c>
       <c r="W63">
-        <v>0.1286994047936257</v>
+        <v>0.1289913498775994</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.8220070484275364</v>
+        <v>0.8087488702270922</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1375509758069035</v>
+        <v>0.1734596186811558</v>
       </c>
       <c r="C64">
-        <v>-101.8711382067794</v>
+        <v>-233.3563763508855</v>
       </c>
       <c r="D64">
-        <v>435.7308617932205</v>
+        <v>313.1666236491145</v>
       </c>
       <c r="E64">
-        <v>-149.698</v>
+        <v>-140.777</v>
       </c>
       <c r="F64">
-        <v>553.102</v>
+        <v>562.0229999999999</v>
       </c>
       <c r="G64">
         <v>15.5</v>
@@ -6535,45 +6535,45 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M64">
-        <v>81.19537360000001</v>
+        <v>112.8542184</v>
       </c>
       <c r="N64">
-        <v>-15.52870693333334</v>
+        <v>-47.18755173333331</v>
       </c>
       <c r="O64">
-        <v>-2.329306040000001</v>
+        <v>-7.078132759999996</v>
       </c>
       <c r="P64">
-        <v>-13.19940089333334</v>
+        <v>-40.10941897333331</v>
       </c>
       <c r="Q64">
-        <v>15.80059910666666</v>
+        <v>-11.10941897333331</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1515166812705047</v>
+        <v>0.1567485993433625</v>
       </c>
       <c r="T64">
-        <v>2.005406378970927</v>
+        <v>2.104653931499702</v>
       </c>
       <c r="U64">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1213123305340638</v>
+        <v>0.08728074271081038</v>
       </c>
       <c r="W64">
-        <v>0.1289913498775994</v>
+        <v>0.1832740268636693</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y64">
-        <v>0.8087488702270922</v>
+        <v>0.5818716180720692</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1734596186811558</v>
+        <v>0.1750096186811558</v>
       </c>
       <c r="C65">
-        <v>-233.3563763508855</v>
+        <v>-246.0341265960353</v>
       </c>
       <c r="D65">
-        <v>313.1666236491145</v>
+        <v>309.4098734039647</v>
       </c>
       <c r="E65">
-        <v>-140.777</v>
+        <v>-131.856</v>
       </c>
       <c r="F65">
-        <v>562.0229999999999</v>
+        <v>570.944</v>
       </c>
       <c r="G65">
         <v>15.5</v>
@@ -6617,37 +6617,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M65">
-        <v>112.8542184</v>
+        <v>114.6455552</v>
       </c>
       <c r="N65">
-        <v>-47.18755173333331</v>
+        <v>-48.97888853333332</v>
       </c>
       <c r="O65">
-        <v>-7.078132759999996</v>
+        <v>-7.346833279999998</v>
       </c>
       <c r="P65">
-        <v>-40.10941897333331</v>
+        <v>-41.63205525333332</v>
       </c>
       <c r="Q65">
-        <v>-11.10941897333331</v>
+        <v>-12.63205525333332</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1567485993433625</v>
+        <v>0.1598305048806781</v>
       </c>
       <c r="T65">
-        <v>2.104653931499702</v>
+        <v>2.163116540708027</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.08728074271081038</v>
+        <v>0.08591698110595396</v>
       </c>
       <c r="W65">
-        <v>0.1832740268636693</v>
+        <v>0.1835478701939245</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5818716180720692</v>
+        <v>0.572779874039693</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1750096186811558</v>
+        <v>0.1765596186811557</v>
       </c>
       <c r="C66">
-        <v>-246.0341265960353</v>
+        <v>-258.6228132152931</v>
       </c>
       <c r="D66">
-        <v>309.4098734039647</v>
+        <v>305.7421867847069</v>
       </c>
       <c r="E66">
-        <v>-131.856</v>
+        <v>-122.9349999999999</v>
       </c>
       <c r="F66">
-        <v>570.944</v>
+        <v>579.865</v>
       </c>
       <c r="G66">
         <v>15.5</v>
@@ -6699,37 +6699,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M66">
-        <v>114.6455552</v>
+        <v>116.436892</v>
       </c>
       <c r="N66">
-        <v>-48.97888853333332</v>
+        <v>-50.77022533333333</v>
       </c>
       <c r="O66">
-        <v>-7.346833279999998</v>
+        <v>-7.615533799999999</v>
       </c>
       <c r="P66">
-        <v>-41.63205525333332</v>
+        <v>-43.15469153333333</v>
       </c>
       <c r="Q66">
-        <v>-12.63205525333332</v>
+        <v>-14.15469153333333</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1598305048806781</v>
+        <v>0.1630885193058403</v>
       </c>
       <c r="T66">
-        <v>2.163116540708027</v>
+        <v>2.224919870442542</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.08591698110595396</v>
+        <v>0.08459518139663157</v>
       </c>
       <c r="W66">
-        <v>0.1835478701939245</v>
+        <v>0.1838132875755564</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.572779874039693</v>
+        <v>0.5639678759775439</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1765596186811557</v>
+        <v>0.1781096186811557</v>
       </c>
       <c r="C67">
-        <v>-258.6228132152931</v>
+        <v>-271.125566335286</v>
       </c>
       <c r="D67">
-        <v>305.7421867847069</v>
+        <v>302.160433664714</v>
       </c>
       <c r="E67">
-        <v>-122.9349999999999</v>
+        <v>-114.014</v>
       </c>
       <c r="F67">
-        <v>579.865</v>
+        <v>588.7859999999999</v>
       </c>
       <c r="G67">
         <v>15.5</v>
@@ -6781,37 +6781,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M67">
-        <v>116.436892</v>
+        <v>118.2282288</v>
       </c>
       <c r="N67">
-        <v>-50.77022533333333</v>
+        <v>-52.56156213333333</v>
       </c>
       <c r="O67">
-        <v>-7.615533799999999</v>
+        <v>-7.884234319999998</v>
       </c>
       <c r="P67">
-        <v>-43.15469153333333</v>
+        <v>-44.67732781333333</v>
       </c>
       <c r="Q67">
-        <v>-14.15469153333333</v>
+        <v>-15.67732781333333</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1630885193058403</v>
+        <v>0.166538181638365</v>
       </c>
       <c r="T67">
-        <v>2.224919870442542</v>
+        <v>2.290358690161441</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.08459518139663157</v>
+        <v>0.08331343622395534</v>
       </c>
       <c r="W67">
-        <v>0.1838132875755564</v>
+        <v>0.1840706620062298</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5639678759775439</v>
+        <v>0.5554229081597023</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1781096186811557</v>
+        <v>0.1796596186811558</v>
       </c>
       <c r="C68">
-        <v>-271.125566335286</v>
+        <v>-283.5453711040033</v>
       </c>
       <c r="D68">
-        <v>302.160433664714</v>
+        <v>298.6616288959967</v>
       </c>
       <c r="E68">
-        <v>-114.014</v>
+        <v>-105.093</v>
       </c>
       <c r="F68">
-        <v>588.7859999999999</v>
+        <v>597.707</v>
       </c>
       <c r="G68">
         <v>15.5</v>
@@ -6863,37 +6863,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M68">
-        <v>118.2282288</v>
+        <v>120.0195656</v>
       </c>
       <c r="N68">
-        <v>-52.56156213333333</v>
+        <v>-54.35289893333334</v>
       </c>
       <c r="O68">
-        <v>-7.884234319999998</v>
+        <v>-8.15293484</v>
       </c>
       <c r="P68">
-        <v>-44.67732781333333</v>
+        <v>-46.19996409333334</v>
       </c>
       <c r="Q68">
-        <v>-15.67732781333333</v>
+        <v>-17.19996409333334</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.166538181638365</v>
+        <v>0.1701969144152852</v>
       </c>
       <c r="T68">
-        <v>2.290358690161441</v>
+        <v>2.359763498954212</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.08331343622395534</v>
+        <v>0.08206995210120974</v>
       </c>
       <c r="W68">
-        <v>0.1840706620062298</v>
+        <v>0.1843203536180771</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5554229081597023</v>
+        <v>0.5471330140080649</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1796596186811558</v>
+        <v>0.1812096186811558</v>
       </c>
       <c r="C69">
-        <v>-283.5453711040033</v>
+        <v>-295.8850759884681</v>
       </c>
       <c r="D69">
-        <v>298.6616288959967</v>
+        <v>295.2429240115318</v>
       </c>
       <c r="E69">
-        <v>-105.093</v>
+        <v>-96.17200000000003</v>
       </c>
       <c r="F69">
-        <v>597.707</v>
+        <v>606.6279999999999</v>
       </c>
       <c r="G69">
         <v>15.5</v>
@@ -6945,37 +6945,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M69">
-        <v>120.0195656</v>
+        <v>121.8109024</v>
       </c>
       <c r="N69">
-        <v>-54.35289893333334</v>
+        <v>-56.14423573333332</v>
       </c>
       <c r="O69">
-        <v>-8.15293484</v>
+        <v>-8.421635359999998</v>
       </c>
       <c r="P69">
-        <v>-46.19996409333334</v>
+        <v>-47.72260037333332</v>
       </c>
       <c r="Q69">
-        <v>-17.19996409333334</v>
+        <v>-18.72260037333332</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1701969144152852</v>
+        <v>0.1740843179907629</v>
       </c>
       <c r="T69">
-        <v>2.359763498954212</v>
+        <v>2.433506108296531</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.08206995210120974</v>
+        <v>0.08086304104089784</v>
       </c>
       <c r="W69">
-        <v>0.1843203536180771</v>
+        <v>0.1845627013589877</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5471330140080649</v>
+        <v>0.5390869402726524</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1812096186811558</v>
+        <v>0.1827596186811558</v>
       </c>
       <c r="C70">
-        <v>-295.8850759884681</v>
+        <v>-308.1474005089697</v>
       </c>
       <c r="D70">
-        <v>295.2429240115318</v>
+        <v>291.9015994910303</v>
       </c>
       <c r="E70">
-        <v>-96.17200000000003</v>
+        <v>-87.25099999999998</v>
       </c>
       <c r="F70">
-        <v>606.6279999999999</v>
+        <v>615.549</v>
       </c>
       <c r="G70">
         <v>15.5</v>
@@ -7027,37 +7027,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M70">
-        <v>121.8109024</v>
+        <v>123.6022392</v>
       </c>
       <c r="N70">
-        <v>-56.14423573333332</v>
+        <v>-57.93557253333333</v>
       </c>
       <c r="O70">
-        <v>-8.421635359999998</v>
+        <v>-8.690335879999999</v>
       </c>
       <c r="P70">
-        <v>-47.72260037333332</v>
+        <v>-49.24523665333333</v>
       </c>
       <c r="Q70">
-        <v>-18.72260037333332</v>
+        <v>-20.24523665333333</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1740843179907629</v>
+        <v>0.1782225217969165</v>
       </c>
       <c r="T70">
-        <v>2.433506108296531</v>
+        <v>2.512006305338355</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.08086304104089784</v>
+        <v>0.07969111290987033</v>
       </c>
       <c r="W70">
-        <v>0.1845627013589877</v>
+        <v>0.1847980245276981</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5390869402726524</v>
+        <v>0.5312740860658023</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1827596186811558</v>
+        <v>0.1843096186811558</v>
       </c>
       <c r="C71">
-        <v>-308.1474005089697</v>
+        <v>-320.3349424539924</v>
       </c>
       <c r="D71">
-        <v>291.9015994910303</v>
+        <v>288.6350575460076</v>
       </c>
       <c r="E71">
-        <v>-87.25099999999998</v>
+        <v>-78.32999999999993</v>
       </c>
       <c r="F71">
-        <v>615.549</v>
+        <v>624.47</v>
       </c>
       <c r="G71">
         <v>15.5</v>
@@ -7109,37 +7109,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M71">
-        <v>123.6022392</v>
+        <v>125.393576</v>
       </c>
       <c r="N71">
-        <v>-57.93557253333333</v>
+        <v>-59.72690933333334</v>
       </c>
       <c r="O71">
-        <v>-8.690335879999999</v>
+        <v>-8.9590364</v>
       </c>
       <c r="P71">
-        <v>-49.24523665333333</v>
+        <v>-50.76787293333334</v>
       </c>
       <c r="Q71">
-        <v>-20.24523665333333</v>
+        <v>-21.76787293333334</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1782225217969165</v>
+        <v>0.1826366058568137</v>
       </c>
       <c r="T71">
-        <v>2.512006305338355</v>
+        <v>2.595739848849633</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.07969111290987033</v>
+        <v>0.07855266843972931</v>
       </c>
       <c r="W71">
-        <v>0.1847980245276981</v>
+        <v>0.1850266241773024</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.5312740860658023</v>
+        <v>0.5236844562648622</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1843096186811558</v>
+        <v>0.1858596186811558</v>
       </c>
       <c r="C72">
-        <v>-320.3349424539924</v>
+        <v>-332.4501846160732</v>
       </c>
       <c r="D72">
-        <v>288.6350575460076</v>
+        <v>285.4408153839267</v>
       </c>
       <c r="E72">
-        <v>-78.32999999999993</v>
+        <v>-69.40899999999999</v>
       </c>
       <c r="F72">
-        <v>624.47</v>
+        <v>633.391</v>
       </c>
       <c r="G72">
         <v>15.5</v>
@@ -7191,37 +7191,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M72">
-        <v>125.393576</v>
+        <v>127.1849128</v>
       </c>
       <c r="N72">
-        <v>-59.72690933333334</v>
+        <v>-61.51824613333332</v>
       </c>
       <c r="O72">
-        <v>-8.9590364</v>
+        <v>-9.227736919999998</v>
       </c>
       <c r="P72">
-        <v>-50.76787293333334</v>
+        <v>-52.29050921333332</v>
       </c>
       <c r="Q72">
-        <v>-21.76787293333334</v>
+        <v>-23.29050921333332</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1826366058568137</v>
+        <v>0.1873551095070487</v>
       </c>
       <c r="T72">
-        <v>2.595739848849633</v>
+        <v>2.685248119499621</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.07855266843972931</v>
+        <v>0.07744629282790216</v>
       </c>
       <c r="W72">
-        <v>0.1850266241773024</v>
+        <v>0.1852487844001572</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.5236844562648622</v>
+        <v>0.5163086188526811</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1858596186811557</v>
+        <v>0.1874096186811557</v>
       </c>
       <c r="C73">
-        <v>-332.450184616073</v>
+        <v>-344.4955010852902</v>
       </c>
       <c r="D73">
-        <v>285.4408153839269</v>
+        <v>282.3164989147097</v>
       </c>
       <c r="E73">
-        <v>-69.40900000000011</v>
+        <v>-60.48800000000006</v>
       </c>
       <c r="F73">
-        <v>633.3909999999998</v>
+        <v>642.3119999999999</v>
       </c>
       <c r="G73">
         <v>15.5</v>
@@ -7273,37 +7273,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M73">
-        <v>127.1849128</v>
+        <v>128.9762496</v>
       </c>
       <c r="N73">
-        <v>-61.51824613333331</v>
+        <v>-63.30958293333332</v>
       </c>
       <c r="O73">
-        <v>-9.227736919999996</v>
+        <v>-9.496437439999998</v>
       </c>
       <c r="P73">
-        <v>-52.29050921333331</v>
+        <v>-53.81314549333332</v>
       </c>
       <c r="Q73">
-        <v>-23.29050921333331</v>
+        <v>-24.81314549333332</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1873551095070487</v>
+        <v>0.1924106491323004</v>
       </c>
       <c r="T73">
-        <v>2.68524811949962</v>
+        <v>2.781149838053178</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.07744629282790216</v>
+        <v>0.07637064987195907</v>
       </c>
       <c r="W73">
-        <v>0.1852487844001572</v>
+        <v>0.1854647735057106</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.5163086188526811</v>
+        <v>0.5091376658130604</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1874096186811557</v>
+        <v>0.1889596186811558</v>
       </c>
       <c r="C74">
-        <v>-344.4955010852902</v>
+        <v>-356.4731631339117</v>
       </c>
       <c r="D74">
-        <v>282.3164989147097</v>
+        <v>279.2598368660882</v>
       </c>
       <c r="E74">
-        <v>-60.48800000000006</v>
+        <v>-51.56700000000001</v>
       </c>
       <c r="F74">
-        <v>642.3119999999999</v>
+        <v>651.2329999999999</v>
       </c>
       <c r="G74">
         <v>15.5</v>
@@ -7355,37 +7355,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M74">
-        <v>128.9762496</v>
+        <v>130.7675864</v>
       </c>
       <c r="N74">
-        <v>-63.30958293333332</v>
+        <v>-65.10091973333333</v>
       </c>
       <c r="O74">
-        <v>-9.496437439999998</v>
+        <v>-9.765137959999999</v>
       </c>
       <c r="P74">
-        <v>-53.81314549333332</v>
+        <v>-55.33578177333333</v>
       </c>
       <c r="Q74">
-        <v>-24.81314549333332</v>
+        <v>-26.33578177333333</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1924106491323004</v>
+        <v>0.1978406731742375</v>
       </c>
       <c r="T74">
-        <v>2.781149838053178</v>
+        <v>2.884155387610703</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.07637064987195907</v>
+        <v>0.07532447658604181</v>
       </c>
       <c r="W74">
-        <v>0.1854647735057106</v>
+        <v>0.1856748451015228</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5091376658130604</v>
+        <v>0.5021631772402788</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1889596186811558</v>
+        <v>0.2167641616937456</v>
       </c>
       <c r="C75">
-        <v>-356.4731631339117</v>
+        <v>-410.811238086387</v>
       </c>
       <c r="D75">
-        <v>279.2598368660882</v>
+        <v>233.8427619136129</v>
       </c>
       <c r="E75">
-        <v>-51.56700000000001</v>
+        <v>-42.64600000000007</v>
       </c>
       <c r="F75">
-        <v>651.2329999999999</v>
+        <v>660.1539999999999</v>
       </c>
       <c r="G75">
         <v>15.5</v>
@@ -7437,45 +7437,45 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M75">
-        <v>130.7675864</v>
+        <v>155.6643132</v>
       </c>
       <c r="N75">
-        <v>-65.10091973333333</v>
+        <v>-89.99764653333331</v>
       </c>
       <c r="O75">
-        <v>-9.765137959999999</v>
+        <v>-13.49964698</v>
       </c>
       <c r="P75">
-        <v>-55.33578177333333</v>
+        <v>-76.49799955333332</v>
       </c>
       <c r="Q75">
-        <v>-26.33578177333333</v>
+        <v>-47.49799955333332</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1978406731742375</v>
+        <v>0.2050520183447458</v>
       </c>
       <c r="T75">
-        <v>2.884155387610703</v>
+        <v>3.020951940738345</v>
       </c>
       <c r="U75">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.07532447658604181</v>
+        <v>0.06327718792774657</v>
       </c>
       <c r="W75">
-        <v>0.1856748451015228</v>
+        <v>0.2208792390866374</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y75">
-        <v>0.5021631772402788</v>
+        <v>0.4218479195183105</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2167641616937456</v>
+        <v>0.2186641616937456</v>
       </c>
       <c r="C76">
-        <v>-410.811238086387</v>
+        <v>-422.3024715187107</v>
       </c>
       <c r="D76">
-        <v>233.8427619136129</v>
+        <v>231.2725284812892</v>
       </c>
       <c r="E76">
-        <v>-42.64600000000007</v>
+        <v>-33.72500000000002</v>
       </c>
       <c r="F76">
-        <v>660.1539999999999</v>
+        <v>669.0749999999999</v>
       </c>
       <c r="G76">
         <v>15.5</v>
@@ -7519,37 +7519,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M76">
-        <v>155.6643132</v>
+        <v>157.767885</v>
       </c>
       <c r="N76">
-        <v>-89.99764653333331</v>
+        <v>-92.10121833333331</v>
       </c>
       <c r="O76">
-        <v>-13.49964698</v>
+        <v>-13.81518275</v>
       </c>
       <c r="P76">
-        <v>-76.49799955333332</v>
+        <v>-78.28603558333332</v>
       </c>
       <c r="Q76">
-        <v>-47.49799955333332</v>
+        <v>-49.28603558333332</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2050520183447458</v>
+        <v>0.2114220990785357</v>
       </c>
       <c r="T76">
-        <v>3.020951940738345</v>
+        <v>3.141790018367879</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.06327718792774657</v>
+        <v>0.06243349208870995</v>
       </c>
       <c r="W76">
-        <v>0.2208792390866374</v>
+        <v>0.2210781825654822</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4218479195183105</v>
+        <v>0.4162232805913997</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2186641616937456</v>
+        <v>0.2205641616937456</v>
       </c>
       <c r="C77">
-        <v>-422.3024715187107</v>
+        <v>-433.7378188531744</v>
       </c>
       <c r="D77">
-        <v>231.2725284812892</v>
+        <v>228.7581811468256</v>
       </c>
       <c r="E77">
-        <v>-33.72500000000002</v>
+        <v>-24.80399999999997</v>
       </c>
       <c r="F77">
-        <v>669.0749999999999</v>
+        <v>677.996</v>
       </c>
       <c r="G77">
         <v>15.5</v>
@@ -7601,37 +7601,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M77">
-        <v>157.767885</v>
+        <v>159.8714568</v>
       </c>
       <c r="N77">
-        <v>-92.10121833333331</v>
+        <v>-94.20479013333333</v>
       </c>
       <c r="O77">
-        <v>-13.81518275</v>
+        <v>-14.13071852</v>
       </c>
       <c r="P77">
-        <v>-78.28603558333332</v>
+        <v>-80.07407161333333</v>
       </c>
       <c r="Q77">
-        <v>-49.28603558333332</v>
+        <v>-51.07407161333333</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2114220990785357</v>
+        <v>0.2183230198734746</v>
       </c>
       <c r="T77">
-        <v>3.141790018367879</v>
+        <v>3.272697935799874</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06243349208870995</v>
+        <v>0.06161199877175323</v>
       </c>
       <c r="W77">
-        <v>0.2210781825654822</v>
+        <v>0.2212718906896206</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.4162232805913997</v>
+        <v>0.4107466584783549</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2205641616937456</v>
+        <v>0.2224641616937456</v>
       </c>
       <c r="C78">
-        <v>-433.7378188531744</v>
+        <v>-445.1190832328419</v>
       </c>
       <c r="D78">
-        <v>228.7581811468256</v>
+        <v>226.2979167671579</v>
       </c>
       <c r="E78">
-        <v>-24.80399999999997</v>
+        <v>-15.88300000000004</v>
       </c>
       <c r="F78">
-        <v>677.996</v>
+        <v>686.9169999999999</v>
       </c>
       <c r="G78">
         <v>15.5</v>
@@ -7683,37 +7683,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M78">
-        <v>159.8714568</v>
+        <v>161.9750286</v>
       </c>
       <c r="N78">
-        <v>-94.20479013333333</v>
+        <v>-96.3083619333333</v>
       </c>
       <c r="O78">
-        <v>-14.13071852</v>
+        <v>-14.44625429</v>
       </c>
       <c r="P78">
-        <v>-80.07407161333333</v>
+        <v>-81.8621076433333</v>
       </c>
       <c r="Q78">
-        <v>-51.07407161333333</v>
+        <v>-52.8621076433333</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2183230198734746</v>
+        <v>0.2258240207375387</v>
       </c>
       <c r="T78">
-        <v>3.272697935799874</v>
+        <v>3.414989150399868</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06161199877175323</v>
+        <v>0.06081184294354865</v>
       </c>
       <c r="W78">
-        <v>0.2212718906896206</v>
+        <v>0.2214605674339112</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.4107466584783549</v>
+        <v>0.4054122862903244</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2224641616937456</v>
+        <v>0.2243641616937456</v>
       </c>
       <c r="C79">
-        <v>-445.1190832328419</v>
+        <v>-456.4479910558857</v>
       </c>
       <c r="D79">
-        <v>226.2979167671579</v>
+        <v>223.8900089441142</v>
       </c>
       <c r="E79">
-        <v>-15.88300000000004</v>
+        <v>-6.961999999999989</v>
       </c>
       <c r="F79">
-        <v>686.9169999999999</v>
+        <v>695.838</v>
       </c>
       <c r="G79">
         <v>15.5</v>
@@ -7765,37 +7765,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M79">
-        <v>161.9750286</v>
+        <v>164.0786004</v>
       </c>
       <c r="N79">
-        <v>-96.3083619333333</v>
+        <v>-98.41193373333333</v>
       </c>
       <c r="O79">
-        <v>-14.44625429</v>
+        <v>-14.76179006</v>
       </c>
       <c r="P79">
-        <v>-81.8621076433333</v>
+        <v>-83.65014367333333</v>
       </c>
       <c r="Q79">
-        <v>-52.8621076433333</v>
+        <v>-54.65014367333333</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2258240207375387</v>
+        <v>0.2340069307710632</v>
       </c>
       <c r="T79">
-        <v>3.414989150399868</v>
+        <v>3.570215929963499</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06081184294354865</v>
+        <v>0.06003220393145187</v>
       </c>
       <c r="W79">
-        <v>0.2214605674339112</v>
+        <v>0.2216444063129637</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.4054122862903244</v>
+        <v>0.4002146928763458</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2243641616937456</v>
+        <v>0.2262641616937456</v>
       </c>
       <c r="C80">
-        <v>-456.4479910558857</v>
+        <v>-467.7261960155924</v>
       </c>
       <c r="D80">
-        <v>223.8900089441142</v>
+        <v>221.5328039844076</v>
       </c>
       <c r="E80">
-        <v>-6.961999999999989</v>
+        <v>1.95900000000006</v>
       </c>
       <c r="F80">
-        <v>695.838</v>
+        <v>704.759</v>
       </c>
       <c r="G80">
         <v>15.5</v>
@@ -7847,37 +7847,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M80">
-        <v>164.0786004</v>
+        <v>166.1821722</v>
       </c>
       <c r="N80">
-        <v>-98.41193373333333</v>
+        <v>-100.5155055333333</v>
       </c>
       <c r="O80">
-        <v>-14.76179006</v>
+        <v>-15.07732583</v>
       </c>
       <c r="P80">
-        <v>-83.65014367333333</v>
+        <v>-85.43817970333333</v>
       </c>
       <c r="Q80">
-        <v>-54.65014367333333</v>
+        <v>-56.43817970333333</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2340069307710632</v>
+        <v>0.2429691655696853</v>
       </c>
       <c r="T80">
-        <v>3.570215929963499</v>
+        <v>3.740226212342714</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06003220393145187</v>
+        <v>0.05927230261586387</v>
       </c>
       <c r="W80">
-        <v>0.2216444063129637</v>
+        <v>0.2218235910431793</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4002146928763458</v>
+        <v>0.3951486841057592</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2262641616937456</v>
+        <v>0.2281641616937455</v>
       </c>
       <c r="C81">
-        <v>-467.7261960155924</v>
+        <v>-478.9552828878213</v>
       </c>
       <c r="D81">
-        <v>221.5328039844076</v>
+        <v>219.2247171121786</v>
       </c>
       <c r="E81">
-        <v>1.95900000000006</v>
+        <v>10.88</v>
       </c>
       <c r="F81">
-        <v>704.759</v>
+        <v>713.6799999999999</v>
       </c>
       <c r="G81">
         <v>15.5</v>
@@ -7929,37 +7929,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M81">
-        <v>166.1821722</v>
+        <v>168.285744</v>
       </c>
       <c r="N81">
-        <v>-100.5155055333333</v>
+        <v>-102.6190773333333</v>
       </c>
       <c r="O81">
-        <v>-15.07732583</v>
+        <v>-15.3928616</v>
       </c>
       <c r="P81">
-        <v>-85.43817970333333</v>
+        <v>-87.22621573333332</v>
       </c>
       <c r="Q81">
-        <v>-56.43817970333333</v>
+        <v>-58.22621573333332</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2429691655696853</v>
+        <v>0.2528276238481695</v>
       </c>
       <c r="T81">
-        <v>3.740226212342714</v>
+        <v>3.927237522959849</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05927230261586387</v>
+        <v>0.05853139883316557</v>
       </c>
       <c r="W81">
-        <v>0.2218235910431793</v>
+        <v>0.2219982961551396</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3951486841057592</v>
+        <v>0.3902093255544372</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2281641616937455</v>
+        <v>0.2300641616937456</v>
       </c>
       <c r="C82">
-        <v>-478.9552828878213</v>
+        <v>-490.1367710841395</v>
       </c>
       <c r="D82">
-        <v>219.2247171121786</v>
+        <v>216.9642289158606</v>
       </c>
       <c r="E82">
-        <v>10.88</v>
+        <v>19.80100000000004</v>
       </c>
       <c r="F82">
-        <v>713.6799999999999</v>
+        <v>722.601</v>
       </c>
       <c r="G82">
         <v>15.5</v>
@@ -8011,37 +8011,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M82">
-        <v>168.285744</v>
+        <v>170.3893158</v>
       </c>
       <c r="N82">
-        <v>-102.6190773333333</v>
+        <v>-104.7226491333333</v>
       </c>
       <c r="O82">
-        <v>-15.3928616</v>
+        <v>-15.70839737</v>
       </c>
       <c r="P82">
-        <v>-87.22621573333332</v>
+        <v>-89.01425176333335</v>
       </c>
       <c r="Q82">
-        <v>-58.22621573333332</v>
+        <v>-60.01425176333335</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2528276238481695</v>
+        <v>0.2637238145770207</v>
       </c>
       <c r="T82">
-        <v>3.927237522959849</v>
+        <v>4.133934234694579</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05853139883316557</v>
+        <v>0.05780878897102772</v>
       </c>
       <c r="W82">
-        <v>0.2219982961551396</v>
+        <v>0.2221686875606317</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3902093255544372</v>
+        <v>0.3853919264735182</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2300641616937456</v>
+        <v>0.2319641616937456</v>
       </c>
       <c r="C83">
-        <v>-490.1367710841395</v>
+        <v>-501.2721179873757</v>
       </c>
       <c r="D83">
-        <v>216.9642289158606</v>
+        <v>214.7498820126242</v>
       </c>
       <c r="E83">
-        <v>19.80100000000004</v>
+        <v>28.72199999999998</v>
       </c>
       <c r="F83">
-        <v>722.601</v>
+        <v>731.5219999999999</v>
       </c>
       <c r="G83">
         <v>15.5</v>
@@ -8093,37 +8093,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M83">
-        <v>170.3893158</v>
+        <v>172.4928876</v>
       </c>
       <c r="N83">
-        <v>-104.7226491333333</v>
+        <v>-106.8262209333333</v>
       </c>
       <c r="O83">
-        <v>-15.70839737</v>
+        <v>-16.02393314</v>
       </c>
       <c r="P83">
-        <v>-89.01425176333335</v>
+        <v>-90.80228779333332</v>
       </c>
       <c r="Q83">
-        <v>-60.01425176333335</v>
+        <v>-61.80228779333332</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2637238145770207</v>
+        <v>0.2758306931646329</v>
       </c>
       <c r="T83">
-        <v>4.133934234694579</v>
+        <v>4.363597247733167</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05780878897102772</v>
+        <v>0.05710380373967373</v>
       </c>
       <c r="W83">
-        <v>0.2221686875606317</v>
+        <v>0.2223349230781849</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3853919264735182</v>
+        <v>0.3806920249311583</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2319641616937456</v>
+        <v>0.2338641616937456</v>
       </c>
       <c r="C84">
-        <v>-501.2721179873757</v>
+        <v>-512.3627220849838</v>
       </c>
       <c r="D84">
-        <v>214.7498820126242</v>
+        <v>212.5802779150161</v>
       </c>
       <c r="E84">
-        <v>28.72199999999998</v>
+        <v>37.64300000000003</v>
       </c>
       <c r="F84">
-        <v>731.5219999999999</v>
+        <v>740.443</v>
       </c>
       <c r="G84">
         <v>15.5</v>
@@ -8175,37 +8175,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M84">
-        <v>172.4928876</v>
+        <v>174.5964594</v>
       </c>
       <c r="N84">
-        <v>-106.8262209333333</v>
+        <v>-108.9297927333333</v>
       </c>
       <c r="O84">
-        <v>-16.02393314</v>
+        <v>-16.33946891</v>
       </c>
       <c r="P84">
-        <v>-90.80228779333332</v>
+        <v>-92.59032382333334</v>
       </c>
       <c r="Q84">
-        <v>-61.80228779333332</v>
+        <v>-63.59032382333334</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2758306931646329</v>
+        <v>0.2893619104096113</v>
       </c>
       <c r="T84">
-        <v>4.363597247733167</v>
+        <v>4.620279438776294</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05710380373967373</v>
+        <v>0.05641580610425596</v>
       </c>
       <c r="W84">
-        <v>0.2223349230781849</v>
+        <v>0.2224971529206164</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3806920249311583</v>
+        <v>0.3761053740283732</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2338641616937456</v>
+        <v>0.2357641616937456</v>
       </c>
       <c r="C85">
-        <v>-512.3627220849838</v>
+        <v>-523.4099259143657</v>
       </c>
       <c r="D85">
-        <v>212.5802779150161</v>
+        <v>210.4540740856344</v>
       </c>
       <c r="E85">
-        <v>37.64300000000003</v>
+        <v>46.56400000000008</v>
       </c>
       <c r="F85">
-        <v>740.443</v>
+        <v>749.364</v>
       </c>
       <c r="G85">
         <v>15.5</v>
@@ -8257,37 +8257,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M85">
-        <v>174.5964594</v>
+        <v>176.7000312</v>
       </c>
       <c r="N85">
-        <v>-108.9297927333333</v>
+        <v>-111.0333645333333</v>
       </c>
       <c r="O85">
-        <v>-16.33946891</v>
+        <v>-16.65500468</v>
       </c>
       <c r="P85">
-        <v>-92.59032382333334</v>
+        <v>-94.37835985333334</v>
       </c>
       <c r="Q85">
-        <v>-63.59032382333334</v>
+        <v>-65.37835985333334</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2893619104096113</v>
+        <v>0.3045845298102121</v>
       </c>
       <c r="T85">
-        <v>4.620279438776294</v>
+        <v>4.909046903699814</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05641580610425596</v>
+        <v>0.05574418936491959</v>
       </c>
       <c r="W85">
-        <v>0.2224971529206164</v>
+        <v>0.222655520147752</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3761053740283732</v>
+        <v>0.371627929099464</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2357641616937455</v>
+        <v>0.2376641616937455</v>
       </c>
       <c r="C86">
-        <v>-523.4099259143655</v>
+        <v>-534.4150188331929</v>
       </c>
       <c r="D86">
-        <v>210.4540740856344</v>
+        <v>208.369981166807</v>
       </c>
       <c r="E86">
-        <v>46.56399999999996</v>
+        <v>55.4849999999999</v>
       </c>
       <c r="F86">
-        <v>749.3639999999999</v>
+        <v>758.2849999999999</v>
       </c>
       <c r="G86">
         <v>15.5</v>
@@ -8339,37 +8339,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M86">
-        <v>176.7000312</v>
+        <v>178.803603</v>
       </c>
       <c r="N86">
-        <v>-111.0333645333333</v>
+        <v>-113.1369363333333</v>
       </c>
       <c r="O86">
-        <v>-16.65500468</v>
+        <v>-16.97054044999999</v>
       </c>
       <c r="P86">
-        <v>-94.37835985333331</v>
+        <v>-96.16639588333331</v>
       </c>
       <c r="Q86">
-        <v>-65.37835985333331</v>
+        <v>-67.16639588333331</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3045845298102119</v>
+        <v>0.3218368317975593</v>
       </c>
       <c r="T86">
-        <v>4.90904690369981</v>
+        <v>5.236316697279798</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.0557441893649196</v>
+        <v>0.05508837537239113</v>
       </c>
       <c r="W86">
-        <v>0.2226555201477519</v>
+        <v>0.2228101610871902</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.371627929099464</v>
+        <v>0.3672558358159409</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2376641616937455</v>
+        <v>0.2395641616937456</v>
       </c>
       <c r="C87">
-        <v>-534.4150188331929</v>
+        <v>-545.3792396267404</v>
       </c>
       <c r="D87">
-        <v>208.369981166807</v>
+        <v>206.3267603732596</v>
       </c>
       <c r="E87">
-        <v>55.4849999999999</v>
+        <v>64.40599999999995</v>
       </c>
       <c r="F87">
-        <v>758.2849999999999</v>
+        <v>767.2059999999999</v>
       </c>
       <c r="G87">
         <v>15.5</v>
@@ -8421,37 +8421,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M87">
-        <v>178.803603</v>
+        <v>180.9071748</v>
       </c>
       <c r="N87">
-        <v>-113.1369363333333</v>
+        <v>-115.2405081333333</v>
       </c>
       <c r="O87">
-        <v>-16.97054044999999</v>
+        <v>-17.28607621999999</v>
       </c>
       <c r="P87">
-        <v>-96.16639588333331</v>
+        <v>-97.95443191333331</v>
       </c>
       <c r="Q87">
-        <v>-67.16639588333331</v>
+        <v>-68.95443191333331</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3218368317975593</v>
+        <v>0.341553748354528</v>
       </c>
       <c r="T87">
-        <v>5.236316697279798</v>
+        <v>5.61033931851407</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05508837537239113</v>
+        <v>0.054447812868061</v>
       </c>
       <c r="W87">
-        <v>0.2228101610871902</v>
+        <v>0.2229612057257112</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3672558358159409</v>
+        <v>0.3629854191204067</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2395641616937456</v>
+        <v>0.2414641616937455</v>
       </c>
       <c r="C88">
-        <v>-545.3792396267404</v>
+        <v>-556.3037789633041</v>
       </c>
       <c r="D88">
-        <v>206.3267603732596</v>
+        <v>204.3232210366959</v>
       </c>
       <c r="E88">
-        <v>64.40599999999995</v>
+        <v>73.327</v>
       </c>
       <c r="F88">
-        <v>767.2059999999999</v>
+        <v>776.127</v>
       </c>
       <c r="G88">
         <v>15.5</v>
@@ -8503,37 +8503,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M88">
-        <v>180.9071748</v>
+        <v>183.0107466</v>
       </c>
       <c r="N88">
-        <v>-115.2405081333333</v>
+        <v>-117.3440799333333</v>
       </c>
       <c r="O88">
-        <v>-17.28607621999999</v>
+        <v>-17.60161199</v>
       </c>
       <c r="P88">
-        <v>-97.95443191333331</v>
+        <v>-99.74246794333334</v>
       </c>
       <c r="Q88">
-        <v>-68.95443191333331</v>
+        <v>-70.74246794333334</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.341553748354528</v>
+        <v>0.3643040366894916</v>
       </c>
       <c r="T88">
-        <v>5.61033931851407</v>
+        <v>6.041903881476689</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.054447812868061</v>
+        <v>0.05382197593854305</v>
       </c>
       <c r="W88">
-        <v>0.2229612057257112</v>
+        <v>0.2231087780736915</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3629854191204067</v>
+        <v>0.3588131729236204</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2414641616937455</v>
+        <v>0.2433641616937456</v>
       </c>
       <c r="C89">
-        <v>-556.3037789633041</v>
+        <v>-567.1897817079391</v>
       </c>
       <c r="D89">
-        <v>204.3232210366959</v>
+        <v>202.3582182920608</v>
       </c>
       <c r="E89">
-        <v>73.327</v>
+        <v>82.24799999999993</v>
       </c>
       <c r="F89">
-        <v>776.127</v>
+        <v>785.0479999999999</v>
       </c>
       <c r="G89">
         <v>15.5</v>
@@ -8585,37 +8585,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M89">
-        <v>183.0107466</v>
+        <v>185.1143184</v>
       </c>
       <c r="N89">
-        <v>-117.3440799333333</v>
+        <v>-119.4476517333333</v>
       </c>
       <c r="O89">
-        <v>-17.60161199</v>
+        <v>-17.91714776</v>
       </c>
       <c r="P89">
-        <v>-99.74246794333334</v>
+        <v>-101.5305039733333</v>
       </c>
       <c r="Q89">
-        <v>-70.74246794333334</v>
+        <v>-72.53050397333331</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3643040366894916</v>
+        <v>0.3908460397469493</v>
       </c>
       <c r="T89">
-        <v>6.041903881476689</v>
+        <v>6.545395871599749</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05382197593854305</v>
+        <v>0.05321036257560507</v>
       </c>
       <c r="W89">
-        <v>0.2231087780736915</v>
+        <v>0.2232529965046723</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3588131729236204</v>
+        <v>0.3547357505040338</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2433641616937456</v>
+        <v>0.2452641616937456</v>
       </c>
       <c r="C90">
-        <v>-567.1897817079391</v>
+        <v>-578.0383491039571</v>
       </c>
       <c r="D90">
-        <v>202.3582182920608</v>
+        <v>200.4306508960428</v>
       </c>
       <c r="E90">
-        <v>82.24799999999993</v>
+        <v>91.16899999999998</v>
       </c>
       <c r="F90">
-        <v>785.0479999999999</v>
+        <v>793.9689999999999</v>
       </c>
       <c r="G90">
         <v>15.5</v>
@@ -8667,37 +8667,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M90">
-        <v>185.1143184</v>
+        <v>187.2178902</v>
       </c>
       <c r="N90">
-        <v>-119.4476517333333</v>
+        <v>-121.5512235333333</v>
       </c>
       <c r="O90">
-        <v>-17.91714776</v>
+        <v>-18.23268353</v>
       </c>
       <c r="P90">
-        <v>-101.5305039733333</v>
+        <v>-103.3185400033333</v>
       </c>
       <c r="Q90">
-        <v>-72.53050397333331</v>
+        <v>-74.31854000333333</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3908460397469493</v>
+        <v>0.4222138615421265</v>
       </c>
       <c r="T90">
-        <v>6.545395871599749</v>
+        <v>7.140431859926998</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05321036257560507</v>
+        <v>0.05261249333318253</v>
       </c>
       <c r="W90">
-        <v>0.2232529965046723</v>
+        <v>0.2233939740720356</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3547357505040338</v>
+        <v>0.3507499555545502</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2452641616937456</v>
+        <v>0.2471641616937456</v>
       </c>
       <c r="C91">
-        <v>-578.0383491039571</v>
+        <v>-588.8505408309222</v>
       </c>
       <c r="D91">
-        <v>200.4306508960428</v>
+        <v>198.5394591690777</v>
       </c>
       <c r="E91">
-        <v>91.16899999999998</v>
+        <v>100.09</v>
       </c>
       <c r="F91">
-        <v>793.9689999999999</v>
+        <v>802.89</v>
       </c>
       <c r="G91">
         <v>15.5</v>
@@ -8749,37 +8749,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M91">
-        <v>187.2178902</v>
+        <v>189.321462</v>
       </c>
       <c r="N91">
-        <v>-121.5512235333333</v>
+        <v>-123.6547953333333</v>
       </c>
       <c r="O91">
-        <v>-18.23268353</v>
+        <v>-18.5482193</v>
       </c>
       <c r="P91">
-        <v>-103.3185400033333</v>
+        <v>-105.1065760333333</v>
       </c>
       <c r="Q91">
-        <v>-74.31854000333333</v>
+        <v>-76.10657603333333</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4222138615421265</v>
+        <v>0.4598552476963392</v>
       </c>
       <c r="T91">
-        <v>7.140431859926998</v>
+        <v>7.8544750459197</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05261249333318253</v>
+        <v>0.05202791007392495</v>
       </c>
       <c r="W91">
-        <v>0.2233939740720356</v>
+        <v>0.2235318188045685</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3507499555545502</v>
+        <v>0.3468527338261663</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2471641616937456</v>
+        <v>0.2490641616937456</v>
       </c>
       <c r="C92">
-        <v>-588.8505408309222</v>
+        <v>-599.6273769472249</v>
       </c>
       <c r="D92">
-        <v>198.5394591690777</v>
+        <v>196.6836230527751</v>
       </c>
       <c r="E92">
-        <v>100.09</v>
+        <v>109.011</v>
       </c>
       <c r="F92">
-        <v>802.89</v>
+        <v>811.8109999999999</v>
       </c>
       <c r="G92">
         <v>15.5</v>
@@ -8831,37 +8831,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M92">
-        <v>189.321462</v>
+        <v>191.4250338</v>
       </c>
       <c r="N92">
-        <v>-123.6547953333333</v>
+        <v>-125.7583671333333</v>
       </c>
       <c r="O92">
-        <v>-18.5482193</v>
+        <v>-18.86375507</v>
       </c>
       <c r="P92">
-        <v>-105.1065760333333</v>
+        <v>-106.8946120633333</v>
       </c>
       <c r="Q92">
-        <v>-76.10657603333333</v>
+        <v>-77.89461206333333</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4598552476963392</v>
+        <v>0.5058613863292658</v>
       </c>
       <c r="T92">
-        <v>7.8544750459197</v>
+        <v>8.727194495466334</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05202791007392495</v>
+        <v>0.05145617479838731</v>
       </c>
       <c r="W92">
-        <v>0.2235318188045685</v>
+        <v>0.2236666339825403</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3468527338261663</v>
+        <v>0.3430411653225821</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2490641616937456</v>
+        <v>0.2509641616937456</v>
       </c>
       <c r="C93">
-        <v>-599.6273769472249</v>
+        <v>-610.3698397247158</v>
       </c>
       <c r="D93">
-        <v>196.6836230527751</v>
+        <v>194.8621602752842</v>
       </c>
       <c r="E93">
-        <v>109.011</v>
+        <v>117.932</v>
       </c>
       <c r="F93">
-        <v>811.8109999999999</v>
+        <v>820.732</v>
       </c>
       <c r="G93">
         <v>15.5</v>
@@ -8913,37 +8913,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M93">
-        <v>191.4250338</v>
+        <v>193.5286056</v>
       </c>
       <c r="N93">
-        <v>-125.7583671333333</v>
+        <v>-127.8619389333333</v>
       </c>
       <c r="O93">
-        <v>-18.86375507</v>
+        <v>-19.17929084</v>
       </c>
       <c r="P93">
-        <v>-106.8946120633333</v>
+        <v>-108.6826480933333</v>
       </c>
       <c r="Q93">
-        <v>-77.89461206333333</v>
+        <v>-79.68264809333333</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5058613863292658</v>
+        <v>0.5633690596204241</v>
       </c>
       <c r="T93">
-        <v>8.727194495466334</v>
+        <v>9.818093807399627</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05145617479838731</v>
+        <v>0.05089686855057876</v>
       </c>
       <c r="W93">
-        <v>0.2236666339825403</v>
+        <v>0.2237985183957736</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3430411653225821</v>
+        <v>0.3393124570038584</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2509641616937456</v>
+        <v>0.2528641616937456</v>
       </c>
       <c r="C94">
-        <v>-610.3698397247158</v>
+        <v>-621.0788753823331</v>
       </c>
       <c r="D94">
-        <v>194.8621602752842</v>
+        <v>193.0741246176669</v>
       </c>
       <c r="E94">
-        <v>117.932</v>
+        <v>126.853</v>
       </c>
       <c r="F94">
-        <v>820.732</v>
+        <v>829.6529999999999</v>
       </c>
       <c r="G94">
         <v>15.5</v>
@@ -8995,37 +8995,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M94">
-        <v>193.5286056</v>
+        <v>195.6321774</v>
       </c>
       <c r="N94">
-        <v>-127.8619389333333</v>
+        <v>-129.9655107333333</v>
       </c>
       <c r="O94">
-        <v>-19.17929084</v>
+        <v>-19.49482660999999</v>
       </c>
       <c r="P94">
-        <v>-108.6826480933333</v>
+        <v>-110.4706841233333</v>
       </c>
       <c r="Q94">
-        <v>-79.68264809333333</v>
+        <v>-81.47068412333331</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5633690596204241</v>
+        <v>0.6373074967090563</v>
       </c>
       <c r="T94">
-        <v>9.818093807399627</v>
+        <v>11.22067863702815</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05089686855057876</v>
+        <v>0.05034959039412092</v>
       </c>
       <c r="W94">
-        <v>0.2237985183957736</v>
+        <v>0.2239275665850663</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3393124570038584</v>
+        <v>0.3356639359608062</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2528641616937456</v>
+        <v>0.2547641616937455</v>
       </c>
       <c r="C95">
-        <v>-621.0788753823331</v>
+        <v>-631.7553957251524</v>
       </c>
       <c r="D95">
-        <v>193.0741246176669</v>
+        <v>191.3186042748476</v>
       </c>
       <c r="E95">
-        <v>126.853</v>
+        <v>135.774</v>
       </c>
       <c r="F95">
-        <v>829.6529999999999</v>
+        <v>838.574</v>
       </c>
       <c r="G95">
         <v>15.5</v>
@@ -9077,37 +9077,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M95">
-        <v>195.6321774</v>
+        <v>197.7357492</v>
       </c>
       <c r="N95">
-        <v>-129.9655107333333</v>
+        <v>-132.0690825333333</v>
       </c>
       <c r="O95">
-        <v>-19.49482660999999</v>
+        <v>-19.81036237999999</v>
       </c>
       <c r="P95">
-        <v>-110.4706841233333</v>
+        <v>-112.2587201533333</v>
       </c>
       <c r="Q95">
-        <v>-81.47068412333331</v>
+        <v>-83.25872015333331</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6373074967090563</v>
+        <v>0.735892079493899</v>
       </c>
       <c r="T95">
-        <v>11.22067863702815</v>
+        <v>13.09079174319951</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05034959039412092</v>
+        <v>0.04981395645375794</v>
       </c>
       <c r="W95">
-        <v>0.2239275665850663</v>
+        <v>0.2240538690682039</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3356639359608062</v>
+        <v>0.332093043025053</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2547641616937455</v>
+        <v>0.2566641616937456</v>
       </c>
       <c r="C96">
-        <v>-631.7553957251524</v>
+        <v>-642.4002796948247</v>
       </c>
       <c r="D96">
-        <v>191.3186042748476</v>
+        <v>189.5947203051753</v>
       </c>
       <c r="E96">
-        <v>135.774</v>
+        <v>144.6950000000001</v>
       </c>
       <c r="F96">
-        <v>838.574</v>
+        <v>847.495</v>
       </c>
       <c r="G96">
         <v>15.5</v>
@@ -9159,37 +9159,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M96">
-        <v>197.7357492</v>
+        <v>199.839321</v>
       </c>
       <c r="N96">
-        <v>-132.0690825333333</v>
+        <v>-134.1726543333334</v>
       </c>
       <c r="O96">
-        <v>-19.81036237999999</v>
+        <v>-20.12589815</v>
       </c>
       <c r="P96">
-        <v>-112.2587201533333</v>
+        <v>-114.0467561833334</v>
       </c>
       <c r="Q96">
-        <v>-83.25872015333331</v>
+        <v>-85.04675618333336</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.735892079493899</v>
+        <v>0.8739104953926793</v>
       </c>
       <c r="T96">
-        <v>13.09079174319951</v>
+        <v>15.70895009183942</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04981395645375794</v>
+        <v>0.04928959901740258</v>
       </c>
       <c r="W96">
-        <v>0.2240538690682039</v>
+        <v>0.2241775125516965</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.332093043025053</v>
+        <v>0.3285973267826838</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2566641616937456</v>
+        <v>0.2585641616937456</v>
       </c>
       <c r="C97">
-        <v>-642.4002796948247</v>
+        <v>-653.0143748369394</v>
       </c>
       <c r="D97">
-        <v>189.5947203051753</v>
+        <v>187.9016251630605</v>
       </c>
       <c r="E97">
-        <v>144.6950000000001</v>
+        <v>153.616</v>
       </c>
       <c r="F97">
-        <v>847.495</v>
+        <v>856.4159999999999</v>
       </c>
       <c r="G97">
         <v>15.5</v>
@@ -9241,37 +9241,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M97">
-        <v>199.839321</v>
+        <v>201.9428928</v>
       </c>
       <c r="N97">
-        <v>-134.1726543333334</v>
+        <v>-136.2762261333333</v>
       </c>
       <c r="O97">
-        <v>-20.12589815</v>
+        <v>-20.44143391999999</v>
       </c>
       <c r="P97">
-        <v>-114.0467561833334</v>
+        <v>-115.8347922133333</v>
       </c>
       <c r="Q97">
-        <v>-85.04675618333336</v>
+        <v>-86.8347922133333</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8739104953926793</v>
+        <v>1.08093811924085</v>
       </c>
       <c r="T97">
-        <v>15.70895009183942</v>
+        <v>19.63618761479928</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04928959901740258</v>
+        <v>0.04877616569430464</v>
       </c>
       <c r="W97">
-        <v>0.2241775125516965</v>
+        <v>0.224298580129283</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3285973267826838</v>
+        <v>0.325174437962031</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2585641616937455</v>
+        <v>0.2604641616937456</v>
       </c>
       <c r="C98">
-        <v>-653.0143748369394</v>
+        <v>-663.5984986904643</v>
       </c>
       <c r="D98">
-        <v>187.9016251630605</v>
+        <v>186.2385013095355</v>
       </c>
       <c r="E98">
-        <v>153.6159999999999</v>
+        <v>162.5369999999999</v>
       </c>
       <c r="F98">
-        <v>856.4159999999998</v>
+        <v>865.3369999999999</v>
       </c>
       <c r="G98">
         <v>15.5</v>
@@ -9323,37 +9323,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M98">
-        <v>201.9428928</v>
+        <v>204.0464646</v>
       </c>
       <c r="N98">
-        <v>-136.2762261333333</v>
+        <v>-138.3797979333333</v>
       </c>
       <c r="O98">
-        <v>-20.44143391999999</v>
+        <v>-20.75696968999999</v>
       </c>
       <c r="P98">
-        <v>-115.8347922133333</v>
+        <v>-117.6228282433333</v>
       </c>
       <c r="Q98">
-        <v>-86.8347922133333</v>
+        <v>-88.6228282433333</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.080938119240847</v>
+        <v>1.425984158987796</v>
       </c>
       <c r="T98">
-        <v>19.63618761479923</v>
+        <v>26.18158348639897</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04877616569430464</v>
+        <v>0.0482733186252912</v>
       </c>
       <c r="W98">
-        <v>0.224298580129283</v>
+        <v>0.2244171514681564</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.325174437962031</v>
+        <v>0.3218221241686081</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2604641616937456</v>
+        <v>0.2623641616937455</v>
       </c>
       <c r="C99">
-        <v>-663.5984986904643</v>
+        <v>-674.1534401040419</v>
       </c>
       <c r="D99">
-        <v>186.2385013095355</v>
+        <v>184.6045598959579</v>
       </c>
       <c r="E99">
-        <v>162.5369999999999</v>
+        <v>171.458</v>
       </c>
       <c r="F99">
-        <v>865.3369999999999</v>
+        <v>874.2579999999999</v>
       </c>
       <c r="G99">
         <v>15.5</v>
@@ -9405,37 +9405,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M99">
-        <v>204.0464646</v>
+        <v>206.1500364</v>
       </c>
       <c r="N99">
-        <v>-138.3797979333333</v>
+        <v>-140.4833697333333</v>
       </c>
       <c r="O99">
-        <v>-20.75696968999999</v>
+        <v>-21.07250546</v>
       </c>
       <c r="P99">
-        <v>-117.6228282433333</v>
+        <v>-119.4108642733333</v>
       </c>
       <c r="Q99">
-        <v>-88.6228282433333</v>
+        <v>-90.41086427333335</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.425984158987796</v>
+        <v>2.116076238481694</v>
       </c>
       <c r="T99">
-        <v>26.18158348639897</v>
+        <v>39.27237522959846</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.0482733186252912</v>
+        <v>0.04778073374135965</v>
       </c>
       <c r="W99">
-        <v>0.2244171514681564</v>
+        <v>0.2245333029837874</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3218221241686081</v>
+        <v>0.3185382249423976</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2623641616937455</v>
+        <v>0.2642641616937456</v>
       </c>
       <c r="C100">
-        <v>-674.1534401040419</v>
+        <v>-684.6799604835998</v>
       </c>
       <c r="D100">
-        <v>184.6045598959579</v>
+        <v>182.9990395164001</v>
       </c>
       <c r="E100">
-        <v>171.458</v>
+        <v>180.3789999999999</v>
       </c>
       <c r="F100">
-        <v>874.2579999999999</v>
+        <v>883.1789999999999</v>
       </c>
       <c r="G100">
         <v>15.5</v>
@@ -9487,37 +9487,37 @@
         <v>65.66666666666667</v>
       </c>
       <c r="M100">
-        <v>206.1500364</v>
+        <v>208.2536082</v>
       </c>
       <c r="N100">
-        <v>-140.4833697333333</v>
+        <v>-142.5869415333333</v>
       </c>
       <c r="O100">
-        <v>-21.07250546</v>
+        <v>-21.38804122999999</v>
       </c>
       <c r="P100">
-        <v>-119.4108642733333</v>
+        <v>-121.1989003033333</v>
       </c>
       <c r="Q100">
-        <v>-90.41086427333335</v>
+        <v>-92.19890030333329</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.116076238481694</v>
+        <v>4.186352476963387</v>
       </c>
       <c r="T100">
-        <v>39.27237522959846</v>
+        <v>78.54475045919692</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04778073374135965</v>
+        <v>0.04729810006720451</v>
       </c>
       <c r="W100">
-        <v>0.2245333029837874</v>
+        <v>0.2246471080041532</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3185382249423976</v>
+        <v>0.3153206671146969</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2642641616937456</v>
-      </c>
-      <c r="C101">
-        <v>-684.6799604835998</v>
-      </c>
-      <c r="D101">
-        <v>182.9990395164001</v>
-      </c>
-      <c r="E101">
-        <v>180.3789999999999</v>
-      </c>
-      <c r="F101">
-        <v>883.1789999999999</v>
-      </c>
-      <c r="G101">
-        <v>15.5</v>
-      </c>
-      <c r="H101">
-        <v>189.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>94.66666666666667</v>
-      </c>
-      <c r="K101">
-        <v>29</v>
-      </c>
-      <c r="L101">
-        <v>65.66666666666667</v>
-      </c>
-      <c r="M101">
-        <v>208.2536082</v>
-      </c>
-      <c r="N101">
-        <v>-142.5869415333333</v>
-      </c>
-      <c r="O101">
-        <v>-21.38804122999999</v>
-      </c>
-      <c r="P101">
-        <v>-121.1989003033333</v>
-      </c>
-      <c r="Q101">
-        <v>-92.19890030333329</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.186352476963387</v>
-      </c>
-      <c r="T101">
-        <v>78.54475045919692</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04729810006720451</v>
-      </c>
-      <c r="W101">
-        <v>0.2246471080041532</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3153206671146969</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
